--- a/Att.xlsx
+++ b/Att.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\寶可夢\Pokemon_App\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\寶可夢\Pokemon_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A39BC8-E045-4A6E-B74D-889F9E415A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC072A41-E8E7-4FE3-B246-E253608BCCED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -312,6 +312,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="攻守數據"/>
@@ -320,6 +321,7 @@
       <sheetName val="極巨傷害"/>
       <sheetName val="能量點"/>
       <sheetName val="寶可夢圖鑑"/>
+      <sheetName val="天氣加成"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -427,16 +429,16 @@
         </row>
         <row r="8">
           <cell r="AD8" t="str">
-            <v>超極巨顫弦蠑螈</v>
+            <v>卡比獸</v>
           </cell>
           <cell r="AE8" t="str">
-            <v>電</v>
+            <v>一般</v>
           </cell>
           <cell r="AF8" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG8">
-            <v>188</v>
+            <v>149</v>
           </cell>
           <cell r="AH8" t="str">
             <v>G</v>
@@ -444,7 +446,7 @@
         </row>
         <row r="9">
           <cell r="AD9" t="str">
-            <v>顫弦蠑螈</v>
+            <v>超極巨顫弦蠑螈</v>
           </cell>
           <cell r="AE9" t="str">
             <v>電</v>
@@ -456,7 +458,7 @@
             <v>188</v>
           </cell>
           <cell r="AH9" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="10">
@@ -464,7 +466,7 @@
             <v>顫弦蠑螈</v>
           </cell>
           <cell r="AE10" t="str">
-            <v>毒</v>
+            <v>電</v>
           </cell>
           <cell r="AF10" t="str">
             <v>Y</v>
@@ -478,24 +480,24 @@
         </row>
         <row r="11">
           <cell r="AD11" t="str">
-            <v>超極巨妙蛙花</v>
+            <v>顫弦蠑螈</v>
           </cell>
           <cell r="AE11" t="str">
-            <v>草</v>
+            <v>毒</v>
           </cell>
           <cell r="AF11" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG11">
-            <v>159</v>
+            <v>188</v>
           </cell>
           <cell r="AH11" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="12">
           <cell r="AD12" t="str">
-            <v>妙蛙花</v>
+            <v>超極巨妙蛙花</v>
           </cell>
           <cell r="AE12" t="str">
             <v>草</v>
@@ -507,21 +509,21 @@
             <v>159</v>
           </cell>
           <cell r="AH12" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="13">
           <cell r="AD13" t="str">
-            <v>武道熊師(一)</v>
+            <v>妙蛙花</v>
           </cell>
           <cell r="AE13" t="str">
-            <v>格鬥</v>
+            <v>草</v>
           </cell>
           <cell r="AF13" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG13">
-            <v>210</v>
+            <v>159</v>
           </cell>
           <cell r="AH13" t="str">
             <v>D</v>
@@ -529,10 +531,10 @@
         </row>
         <row r="14">
           <cell r="AD14" t="str">
-            <v>武道熊師(連)</v>
+            <v>武道熊師(一)</v>
           </cell>
           <cell r="AE14" t="str">
-            <v>水</v>
+            <v>格鬥</v>
           </cell>
           <cell r="AF14" t="str">
             <v>Y</v>
@@ -546,16 +548,16 @@
         </row>
         <row r="15">
           <cell r="AD15" t="str">
-            <v>閃電鳥</v>
+            <v>武道熊師(連)</v>
           </cell>
           <cell r="AE15" t="str">
-            <v>電</v>
+            <v>水</v>
           </cell>
           <cell r="AF15" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG15">
-            <v>203</v>
+            <v>210</v>
           </cell>
           <cell r="AH15" t="str">
             <v>D</v>
@@ -563,7 +565,7 @@
         </row>
         <row r="16">
           <cell r="AD16" t="str">
-            <v>雷公</v>
+            <v>閃電鳥</v>
           </cell>
           <cell r="AE16" t="str">
             <v>電</v>
@@ -572,7 +574,7 @@
             <v>Y</v>
           </cell>
           <cell r="AG16">
-            <v>194</v>
+            <v>203</v>
           </cell>
           <cell r="AH16" t="str">
             <v>D</v>
@@ -580,16 +582,16 @@
         </row>
         <row r="17">
           <cell r="AD17" t="str">
-            <v>投擲猴</v>
+            <v>雷公</v>
           </cell>
           <cell r="AE17" t="str">
-            <v>格鬥</v>
+            <v>電</v>
           </cell>
           <cell r="AF17" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG17">
-            <v>181</v>
+            <v>194</v>
           </cell>
           <cell r="AH17" t="str">
             <v>D</v>
@@ -597,36 +599,36 @@
         </row>
         <row r="18">
           <cell r="AD18" t="str">
-            <v>超極巨耿鬼</v>
+            <v>投擲猴</v>
           </cell>
           <cell r="AE18" t="str">
-            <v>幽靈</v>
+            <v>格鬥</v>
           </cell>
           <cell r="AF18" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG18">
-            <v>223</v>
+            <v>181</v>
           </cell>
           <cell r="AH18" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="19">
           <cell r="AD19" t="str">
-            <v>耿鬼</v>
+            <v>超極巨耿鬼</v>
           </cell>
           <cell r="AE19" t="str">
-            <v>惡</v>
+            <v>幽靈</v>
           </cell>
           <cell r="AF19" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG19">
             <v>223</v>
           </cell>
           <cell r="AH19" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="20">
@@ -634,10 +636,10 @@
             <v>耿鬼</v>
           </cell>
           <cell r="AE20" t="str">
-            <v>幽靈</v>
+            <v>惡</v>
           </cell>
           <cell r="AF20" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG20">
             <v>223</v>
@@ -648,16 +650,16 @@
         </row>
         <row r="21">
           <cell r="AD21" t="str">
-            <v>蒼響</v>
+            <v>耿鬼</v>
           </cell>
           <cell r="AE21" t="str">
-            <v>鋼</v>
+            <v>幽靈</v>
           </cell>
           <cell r="AF21" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG21">
-            <v>291</v>
+            <v>223</v>
           </cell>
           <cell r="AH21" t="str">
             <v>D</v>
@@ -665,16 +667,16 @@
         </row>
         <row r="22">
           <cell r="AD22" t="str">
-            <v>多刺菊石獸</v>
+            <v>蒼響</v>
           </cell>
           <cell r="AE22" t="str">
-            <v>岩石</v>
+            <v>鋼</v>
           </cell>
           <cell r="AF22" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG22">
-            <v>177</v>
+            <v>291</v>
           </cell>
           <cell r="AH22" t="str">
             <v>D</v>
@@ -682,16 +684,16 @@
         </row>
         <row r="23">
           <cell r="AD23" t="str">
-            <v>妙蛙花</v>
+            <v>多刺菊石獸</v>
           </cell>
           <cell r="AE23" t="str">
-            <v>草</v>
+            <v>岩石</v>
           </cell>
           <cell r="AF23" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG23">
-            <v>159</v>
+            <v>177</v>
           </cell>
           <cell r="AH23" t="str">
             <v>D</v>
@@ -699,16 +701,16 @@
         </row>
         <row r="24">
           <cell r="AD24" t="str">
-            <v>列陣兵</v>
+            <v>妙蛙花</v>
           </cell>
           <cell r="AE24" t="str">
-            <v>格鬥</v>
+            <v>草</v>
           </cell>
           <cell r="AF24" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG24">
-            <v>160</v>
+            <v>159</v>
           </cell>
           <cell r="AH24" t="str">
             <v>D</v>
@@ -716,24 +718,24 @@
         </row>
         <row r="25">
           <cell r="AD25" t="str">
-            <v>超極巨閃焰王牌</v>
+            <v>列陣兵</v>
           </cell>
           <cell r="AE25" t="str">
-            <v>火</v>
+            <v>格鬥</v>
           </cell>
           <cell r="AF25" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG25">
-            <v>205</v>
+            <v>160</v>
           </cell>
           <cell r="AH25" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="26">
           <cell r="AD26" t="str">
-            <v>閃焰王牌</v>
+            <v>超極巨閃焰王牌</v>
           </cell>
           <cell r="AE26" t="str">
             <v>火</v>
@@ -745,21 +747,21 @@
             <v>205</v>
           </cell>
           <cell r="AH26" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="27">
           <cell r="AD27" t="str">
-            <v>鐮刀盔</v>
+            <v>閃焰王牌</v>
           </cell>
           <cell r="AE27" t="str">
-            <v>格鬥</v>
+            <v>火</v>
           </cell>
           <cell r="AF27" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG27">
-            <v>185</v>
+            <v>205</v>
           </cell>
           <cell r="AH27" t="str">
             <v>D</v>
@@ -767,27 +769,27 @@
         </row>
         <row r="28">
           <cell r="AD28" t="str">
-            <v>超極巨噴火龍</v>
+            <v>鐮刀盔</v>
           </cell>
           <cell r="AE28" t="str">
-            <v>火</v>
+            <v>格鬥</v>
           </cell>
           <cell r="AF28" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG28">
-            <v>187</v>
+            <v>185</v>
           </cell>
           <cell r="AH28" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="29">
           <cell r="AD29" t="str">
-            <v>噴火龍</v>
+            <v>超極巨噴火龍</v>
           </cell>
           <cell r="AE29" t="str">
-            <v>飛行</v>
+            <v>火</v>
           </cell>
           <cell r="AF29" t="str">
             <v>Y</v>
@@ -796,7 +798,7 @@
             <v>187</v>
           </cell>
           <cell r="AH29" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="30">
@@ -804,7 +806,7 @@
             <v>噴火龍</v>
           </cell>
           <cell r="AE30" t="str">
-            <v>火</v>
+            <v>飛行</v>
           </cell>
           <cell r="AF30" t="str">
             <v>Y</v>
@@ -821,10 +823,10 @@
             <v>噴火龍</v>
           </cell>
           <cell r="AE31" t="str">
-            <v>龍</v>
+            <v>火</v>
           </cell>
           <cell r="AF31" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG31">
             <v>187</v>
@@ -835,36 +837,36 @@
         </row>
         <row r="32">
           <cell r="AD32" t="str">
-            <v>無極汰那</v>
+            <v>噴火龍</v>
           </cell>
           <cell r="AE32" t="str">
             <v>龍</v>
           </cell>
           <cell r="AF32" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG32">
-            <v>231</v>
+            <v>187</v>
           </cell>
           <cell r="AH32" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="33">
           <cell r="AD33" t="str">
-            <v>拉帝歐斯</v>
+            <v>無極汰那</v>
           </cell>
           <cell r="AE33" t="str">
-            <v>超能力</v>
+            <v>龍</v>
           </cell>
           <cell r="AF33" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG33">
-            <v>221</v>
+            <v>239</v>
           </cell>
           <cell r="AH33" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="34">
@@ -872,7 +874,7 @@
             <v>拉帝歐斯</v>
           </cell>
           <cell r="AE34" t="str">
-            <v>龍</v>
+            <v>超能力</v>
           </cell>
           <cell r="AF34" t="str">
             <v>Y</v>
@@ -886,16 +888,16 @@
         </row>
         <row r="35">
           <cell r="AD35" t="str">
-            <v>狒狒達摩</v>
+            <v>拉帝歐斯</v>
           </cell>
           <cell r="AE35" t="str">
-            <v>火</v>
+            <v>龍</v>
           </cell>
           <cell r="AF35" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG35">
-            <v>218</v>
+            <v>221</v>
           </cell>
           <cell r="AH35" t="str">
             <v>D</v>
@@ -903,16 +905,16 @@
         </row>
         <row r="36">
           <cell r="AD36" t="str">
-            <v>巨金怪</v>
+            <v>狒狒達摩</v>
           </cell>
           <cell r="AE36" t="str">
-            <v>超能力</v>
+            <v>火</v>
           </cell>
           <cell r="AF36" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG36">
-            <v>214</v>
+            <v>218</v>
           </cell>
           <cell r="AH36" t="str">
             <v>D</v>
@@ -923,7 +925,7 @@
             <v>巨金怪</v>
           </cell>
           <cell r="AE37" t="str">
-            <v>鋼</v>
+            <v>超能力</v>
           </cell>
           <cell r="AF37" t="str">
             <v>Y</v>
@@ -940,10 +942,10 @@
             <v>巨金怪</v>
           </cell>
           <cell r="AE38" t="str">
-            <v>蟲</v>
+            <v>鋼</v>
           </cell>
           <cell r="AF38" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG38">
             <v>214</v>
@@ -954,16 +956,16 @@
         </row>
         <row r="39">
           <cell r="AD39" t="str">
-            <v>龍頭地鼠</v>
+            <v>巨金怪</v>
           </cell>
           <cell r="AE39" t="str">
-            <v>地面</v>
+            <v>蟲</v>
           </cell>
           <cell r="AF39" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG39">
-            <v>217</v>
+            <v>214</v>
           </cell>
           <cell r="AH39" t="str">
             <v>D</v>
@@ -974,13 +976,13 @@
             <v>龍頭地鼠</v>
           </cell>
           <cell r="AE40" t="str">
-            <v>鋼</v>
+            <v>地面</v>
           </cell>
           <cell r="AF40" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG40">
-            <v>217</v>
+            <v>220</v>
           </cell>
           <cell r="AH40" t="str">
             <v>D</v>
@@ -988,16 +990,16 @@
         </row>
         <row r="41">
           <cell r="AD41" t="str">
-            <v>武道熊師(一)</v>
+            <v>龍頭地鼠</v>
           </cell>
           <cell r="AE41" t="str">
-            <v>惡</v>
+            <v>鋼</v>
           </cell>
           <cell r="AF41" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG41">
-            <v>210</v>
+            <v>220</v>
           </cell>
           <cell r="AH41" t="str">
             <v>D</v>
@@ -1005,16 +1007,16 @@
         </row>
         <row r="42">
           <cell r="AD42" t="str">
-            <v>閃電鳥</v>
+            <v>武道熊師(一)</v>
           </cell>
           <cell r="AE42" t="str">
-            <v>飛行</v>
+            <v>惡</v>
           </cell>
           <cell r="AF42" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG42">
-            <v>203</v>
+            <v>210</v>
           </cell>
           <cell r="AH42" t="str">
             <v>D</v>
@@ -1022,7 +1024,7 @@
         </row>
         <row r="43">
           <cell r="AD43" t="str">
-            <v>火焰鳥</v>
+            <v>閃電鳥</v>
           </cell>
           <cell r="AE43" t="str">
             <v>飛行</v>
@@ -1031,7 +1033,7 @@
             <v>Y</v>
           </cell>
           <cell r="AG43">
-            <v>200</v>
+            <v>203</v>
           </cell>
           <cell r="AH43" t="str">
             <v>D</v>
@@ -1042,7 +1044,7 @@
             <v>火焰鳥</v>
           </cell>
           <cell r="AE44" t="str">
-            <v>火</v>
+            <v>飛行</v>
           </cell>
           <cell r="AF44" t="str">
             <v>Y</v>
@@ -1056,16 +1058,16 @@
         </row>
         <row r="45">
           <cell r="AD45" t="str">
-            <v>藏瑪然特</v>
+            <v>火焰鳥</v>
           </cell>
           <cell r="AE45" t="str">
-            <v>鋼</v>
+            <v>火</v>
           </cell>
           <cell r="AF45" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG45">
-            <v>218</v>
+            <v>200</v>
           </cell>
           <cell r="AH45" t="str">
             <v>D</v>
@@ -1073,16 +1075,16 @@
         </row>
         <row r="46">
           <cell r="AD46" t="str">
-            <v>炎帝</v>
+            <v>藏瑪然特</v>
           </cell>
           <cell r="AE46" t="str">
-            <v>火</v>
+            <v>鋼</v>
           </cell>
           <cell r="AF46" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG46">
-            <v>175</v>
+            <v>218</v>
           </cell>
           <cell r="AH46" t="str">
             <v>D</v>
@@ -1090,16 +1092,16 @@
         </row>
         <row r="47">
           <cell r="AD47" t="str">
-            <v>布莉姆溫</v>
+            <v>炎帝</v>
           </cell>
           <cell r="AE47" t="str">
-            <v>超能力</v>
+            <v>火</v>
           </cell>
           <cell r="AF47" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG47">
-            <v>198</v>
+            <v>175</v>
           </cell>
           <cell r="AH47" t="str">
             <v>D</v>
@@ -1110,7 +1112,7 @@
             <v>布莉姆溫</v>
           </cell>
           <cell r="AE48" t="str">
-            <v>妖精</v>
+            <v>超能力</v>
           </cell>
           <cell r="AF48" t="str">
             <v>Y</v>
@@ -1124,16 +1126,16 @@
         </row>
         <row r="49">
           <cell r="AD49" t="str">
-            <v>吼鯨王</v>
+            <v>布莉姆溫</v>
           </cell>
           <cell r="AE49" t="str">
-            <v>岩石</v>
+            <v>妖精</v>
           </cell>
           <cell r="AF49" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG49">
-            <v>147</v>
+            <v>198</v>
           </cell>
           <cell r="AH49" t="str">
             <v>D</v>
@@ -1141,16 +1143,16 @@
         </row>
         <row r="50">
           <cell r="AD50" t="str">
-            <v>拉帝亞斯</v>
+            <v>吼鯨王</v>
           </cell>
           <cell r="AE50" t="str">
-            <v>超能力</v>
+            <v>岩石</v>
           </cell>
           <cell r="AF50" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG50">
-            <v>158</v>
+            <v>147</v>
           </cell>
           <cell r="AH50" t="str">
             <v>D</v>
@@ -1161,7 +1163,7 @@
             <v>拉帝亞斯</v>
           </cell>
           <cell r="AE51" t="str">
-            <v>龍</v>
+            <v>超能力</v>
           </cell>
           <cell r="AF51" t="str">
             <v>Y</v>
@@ -1175,16 +1177,16 @@
         </row>
         <row r="52">
           <cell r="AD52" t="str">
-            <v>高傲雉雞</v>
+            <v>拉帝亞斯</v>
           </cell>
           <cell r="AE52" t="str">
-            <v>飛行</v>
+            <v>龍</v>
           </cell>
           <cell r="AF52" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG52">
-            <v>188</v>
+            <v>158</v>
           </cell>
           <cell r="AH52" t="str">
             <v>D</v>
@@ -1192,24 +1194,24 @@
         </row>
         <row r="53">
           <cell r="AD53" t="str">
-            <v>超極巨巴大蝶</v>
+            <v>高傲雉雞</v>
           </cell>
           <cell r="AE53" t="str">
-            <v>蟲</v>
+            <v>飛行</v>
           </cell>
           <cell r="AF53" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG53">
-            <v>143</v>
+            <v>188</v>
           </cell>
           <cell r="AH53" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="54">
           <cell r="AD54" t="str">
-            <v>巴大蝶</v>
+            <v>超極巨巴大蝶</v>
           </cell>
           <cell r="AE54" t="str">
             <v>蟲</v>
@@ -1221,7 +1223,7 @@
             <v>143</v>
           </cell>
           <cell r="AH54" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="55">
@@ -1229,10 +1231,10 @@
             <v>巴大蝶</v>
           </cell>
           <cell r="AE55" t="str">
-            <v>超能力</v>
+            <v>蟲</v>
           </cell>
           <cell r="AF55" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG55">
             <v>143</v>
@@ -1243,16 +1245,16 @@
         </row>
         <row r="56">
           <cell r="AD56" t="str">
-            <v>藏飽栗鼠</v>
+            <v>巴大蝶</v>
           </cell>
           <cell r="AE56" t="str">
-            <v>草</v>
+            <v>超能力</v>
           </cell>
           <cell r="AF56" t="str">
             <v>N</v>
           </cell>
           <cell r="AG56">
-            <v>138</v>
+            <v>143</v>
           </cell>
           <cell r="AH56" t="str">
             <v>D</v>
@@ -1260,16 +1262,16 @@
         </row>
         <row r="57">
           <cell r="AD57" t="str">
-            <v>毛毛角羊</v>
+            <v>藏飽栗鼠</v>
           </cell>
           <cell r="AE57" t="str">
-            <v>格鬥</v>
+            <v>草</v>
           </cell>
           <cell r="AF57" t="str">
             <v>N</v>
           </cell>
           <cell r="AG57">
-            <v>136</v>
+            <v>138</v>
           </cell>
           <cell r="AH57" t="str">
             <v>D</v>
@@ -1277,24 +1279,24 @@
         </row>
         <row r="58">
           <cell r="AD58" t="str">
-            <v>超極巨千面避役</v>
+            <v>毛毛角羊</v>
           </cell>
           <cell r="AE58" t="str">
-            <v>水</v>
+            <v>格鬥</v>
           </cell>
           <cell r="AF58" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG58">
-            <v>217</v>
+            <v>136</v>
           </cell>
           <cell r="AH58" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="59">
           <cell r="AD59" t="str">
-            <v>千面避役</v>
+            <v>超極巨千面避役</v>
           </cell>
           <cell r="AE59" t="str">
             <v>水</v>
@@ -1306,12 +1308,12 @@
             <v>217</v>
           </cell>
           <cell r="AH59" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="60">
           <cell r="AD60" t="str">
-            <v>超極巨巨鉗蟹</v>
+            <v>千面避役</v>
           </cell>
           <cell r="AE60" t="str">
             <v>水</v>
@@ -1320,27 +1322,27 @@
             <v>Y</v>
           </cell>
           <cell r="AG60">
-            <v>198</v>
+            <v>217</v>
           </cell>
           <cell r="AH60" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="61">
           <cell r="AD61" t="str">
-            <v>巨鉗蟹</v>
+            <v>超極巨巨鉗蟹</v>
           </cell>
           <cell r="AE61" t="str">
-            <v>地面</v>
+            <v>水</v>
           </cell>
           <cell r="AF61" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG61">
             <v>198</v>
           </cell>
           <cell r="AH61" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="62">
@@ -1348,7 +1350,7 @@
             <v>巨鉗蟹</v>
           </cell>
           <cell r="AE62" t="str">
-            <v>鋼</v>
+            <v>地面</v>
           </cell>
           <cell r="AF62" t="str">
             <v>N</v>
@@ -1362,7 +1364,7 @@
         </row>
         <row r="63">
           <cell r="AD63" t="str">
-            <v>高傲雉雞</v>
+            <v>巨鉗蟹</v>
           </cell>
           <cell r="AE63" t="str">
             <v>鋼</v>
@@ -1371,7 +1373,7 @@
             <v>N</v>
           </cell>
           <cell r="AG63">
-            <v>188</v>
+            <v>198</v>
           </cell>
           <cell r="AH63" t="str">
             <v>D</v>
@@ -1379,16 +1381,16 @@
         </row>
         <row r="64">
           <cell r="AD64" t="str">
-            <v>鐮刀盔</v>
+            <v>高傲雉雞</v>
           </cell>
           <cell r="AE64" t="str">
-            <v>地面</v>
+            <v>鋼</v>
           </cell>
           <cell r="AF64" t="str">
             <v>N</v>
           </cell>
           <cell r="AG64">
-            <v>185</v>
+            <v>188</v>
           </cell>
           <cell r="AH64" t="str">
             <v>D</v>
@@ -1399,7 +1401,7 @@
             <v>鐮刀盔</v>
           </cell>
           <cell r="AE65" t="str">
-            <v>蟲</v>
+            <v>地面</v>
           </cell>
           <cell r="AF65" t="str">
             <v>N</v>
@@ -1413,16 +1415,16 @@
         </row>
         <row r="66">
           <cell r="AD66" t="str">
-            <v>多刺菊石獸</v>
+            <v>鐮刀盔</v>
           </cell>
           <cell r="AE66" t="str">
-            <v>地面</v>
+            <v>蟲</v>
           </cell>
           <cell r="AF66" t="str">
             <v>N</v>
           </cell>
           <cell r="AG66">
-            <v>177</v>
+            <v>185</v>
           </cell>
           <cell r="AH66" t="str">
             <v>D</v>
@@ -1430,16 +1432,16 @@
         </row>
         <row r="67">
           <cell r="AD67" t="str">
-            <v>巴大蝶</v>
+            <v>多刺菊石獸</v>
           </cell>
           <cell r="AE67" t="str">
-            <v>蟲</v>
+            <v>地面</v>
           </cell>
           <cell r="AF67" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG67">
-            <v>143</v>
+            <v>177</v>
           </cell>
           <cell r="AH67" t="str">
             <v>D</v>
@@ -1447,16 +1449,16 @@
         </row>
         <row r="68">
           <cell r="AD68" t="str">
-            <v>鋼鎧鴉</v>
+            <v>巴大蝶</v>
           </cell>
           <cell r="AE68" t="str">
-            <v>飛行</v>
+            <v>蟲</v>
           </cell>
           <cell r="AF68" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG68">
-            <v>140</v>
+            <v>143</v>
           </cell>
           <cell r="AH68" t="str">
             <v>D</v>
@@ -1467,7 +1469,7 @@
             <v>鋼鎧鴉</v>
           </cell>
           <cell r="AE69" t="str">
-            <v>鋼</v>
+            <v>飛行</v>
           </cell>
           <cell r="AF69" t="str">
             <v>Y</v>
@@ -1484,10 +1486,10 @@
             <v>鋼鎧鴉</v>
           </cell>
           <cell r="AE70" t="str">
-            <v>地面</v>
+            <v>鋼</v>
           </cell>
           <cell r="AF70" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG70">
             <v>140</v>
@@ -1498,50 +1500,50 @@
         </row>
         <row r="71">
           <cell r="AD71" t="str">
-            <v>超極巨灰塵山</v>
+            <v>鋼鎧鴉</v>
           </cell>
           <cell r="AE71" t="str">
-            <v>毒</v>
+            <v>地面</v>
           </cell>
           <cell r="AF71" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG71">
-            <v>153</v>
+            <v>140</v>
           </cell>
           <cell r="AH71" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="72">
           <cell r="AD72" t="str">
-            <v>灰塵山</v>
+            <v>超極巨灰塵山</v>
           </cell>
           <cell r="AE72" t="str">
-            <v>蟲</v>
+            <v>毒</v>
           </cell>
           <cell r="AF72" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG72">
             <v>153</v>
           </cell>
           <cell r="AH72" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="73">
           <cell r="AD73" t="str">
-            <v>吼鯨王</v>
+            <v>灰塵山</v>
           </cell>
           <cell r="AE73" t="str">
-            <v>超能力</v>
+            <v>蟲</v>
           </cell>
           <cell r="AF73" t="str">
             <v>N</v>
           </cell>
           <cell r="AG73">
-            <v>147</v>
+            <v>153</v>
           </cell>
           <cell r="AH73" t="str">
             <v>D</v>
@@ -1549,24 +1551,24 @@
         </row>
         <row r="74">
           <cell r="AD74" t="str">
-            <v>超極巨水箭龜</v>
+            <v>吼鯨王</v>
           </cell>
           <cell r="AE74" t="str">
-            <v>水</v>
+            <v>超能力</v>
           </cell>
           <cell r="AF74" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG74">
-            <v>145</v>
+            <v>147</v>
           </cell>
           <cell r="AH74" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="75">
           <cell r="AD75" t="str">
-            <v>水箭龜</v>
+            <v>超極巨水箭龜</v>
           </cell>
           <cell r="AE75" t="str">
             <v>水</v>
@@ -1578,7 +1580,7 @@
             <v>145</v>
           </cell>
           <cell r="AH75" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="76">
@@ -1586,10 +1588,10 @@
             <v>水箭龜</v>
           </cell>
           <cell r="AE76" t="str">
-            <v>岩石</v>
+            <v>水</v>
           </cell>
           <cell r="AF76" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG76">
             <v>145</v>
@@ -1603,7 +1605,7 @@
             <v>水箭龜</v>
           </cell>
           <cell r="AE77" t="str">
-            <v>惡</v>
+            <v>岩石</v>
           </cell>
           <cell r="AF77" t="str">
             <v>N</v>
@@ -1617,16 +1619,16 @@
         </row>
         <row r="78">
           <cell r="AD78" t="str">
-            <v>勾魂眼</v>
+            <v>水箭龜</v>
           </cell>
           <cell r="AE78" t="str">
-            <v>幽靈</v>
+            <v>惡</v>
           </cell>
           <cell r="AF78" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG78">
-            <v>121</v>
+            <v>145</v>
           </cell>
           <cell r="AH78" t="str">
             <v>D</v>
@@ -1637,7 +1639,7 @@
             <v>勾魂眼</v>
           </cell>
           <cell r="AE79" t="str">
-            <v>惡</v>
+            <v>幽靈</v>
           </cell>
           <cell r="AF79" t="str">
             <v>Y</v>
@@ -1651,16 +1653,16 @@
         </row>
         <row r="80">
           <cell r="AD80" t="str">
-            <v>鐮刀盔</v>
+            <v>勾魂眼</v>
           </cell>
           <cell r="AE80" t="str">
-            <v>水</v>
+            <v>惡</v>
           </cell>
           <cell r="AF80" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG80">
-            <v>185</v>
+            <v>121</v>
           </cell>
           <cell r="AH80" t="str">
             <v>D</v>
@@ -1668,16 +1670,16 @@
         </row>
         <row r="81">
           <cell r="AD81" t="str">
-            <v>藏飽栗鼠</v>
+            <v>鐮刀盔</v>
           </cell>
           <cell r="AE81" t="str">
-            <v>地面</v>
+            <v>水</v>
           </cell>
           <cell r="AF81" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG81">
-            <v>138</v>
+            <v>185</v>
           </cell>
           <cell r="AH81" t="str">
             <v>D</v>
@@ -1688,7 +1690,7 @@
             <v>藏飽栗鼠</v>
           </cell>
           <cell r="AE82" t="str">
-            <v>惡</v>
+            <v>地面</v>
           </cell>
           <cell r="AF82" t="str">
             <v>N</v>
@@ -1702,16 +1704,16 @@
         </row>
         <row r="83">
           <cell r="AD83" t="str">
-            <v>多刺菊石獸</v>
+            <v>藏飽栗鼠</v>
           </cell>
           <cell r="AE83" t="str">
-            <v>水</v>
+            <v>惡</v>
           </cell>
           <cell r="AF83" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG83">
-            <v>177</v>
+            <v>138</v>
           </cell>
           <cell r="AH83" t="str">
             <v>D</v>
@@ -1719,7 +1721,7 @@
         </row>
         <row r="84">
           <cell r="AD84" t="str">
-            <v>水君</v>
+            <v>多刺菊石獸</v>
           </cell>
           <cell r="AE84" t="str">
             <v>水</v>
@@ -1728,7 +1730,7 @@
             <v>Y</v>
           </cell>
           <cell r="AG84">
-            <v>147</v>
+            <v>177</v>
           </cell>
           <cell r="AH84" t="str">
             <v>D</v>
@@ -1736,7 +1738,7 @@
         </row>
         <row r="85">
           <cell r="AD85" t="str">
-            <v>吼鯨王</v>
+            <v>水君</v>
           </cell>
           <cell r="AE85" t="str">
             <v>水</v>
@@ -1753,16 +1755,16 @@
         </row>
         <row r="86">
           <cell r="AD86" t="str">
-            <v>幸福蛋</v>
+            <v>吼鯨王</v>
           </cell>
           <cell r="AE86" t="str">
-            <v>超能力</v>
+            <v>水</v>
           </cell>
           <cell r="AF86" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG86">
-            <v>113</v>
+            <v>147</v>
           </cell>
           <cell r="AH86" t="str">
             <v>D</v>
@@ -1770,16 +1772,16 @@
         </row>
         <row r="87">
           <cell r="AD87" t="str">
-            <v>急凍鳥</v>
+            <v>幸福蛋</v>
           </cell>
           <cell r="AE87" t="str">
-            <v>冰</v>
+            <v>超能力</v>
           </cell>
           <cell r="AF87" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG87">
-            <v>155</v>
+            <v>113</v>
           </cell>
           <cell r="AH87" t="str">
             <v>D</v>
@@ -1787,7 +1789,7 @@
         </row>
         <row r="88">
           <cell r="AD88" t="str">
-            <v>幾何雪花</v>
+            <v>急凍鳥</v>
           </cell>
           <cell r="AE88" t="str">
             <v>冰</v>
@@ -1796,7 +1798,7 @@
             <v>Y</v>
           </cell>
           <cell r="AG88">
-            <v>153</v>
+            <v>155</v>
           </cell>
           <cell r="AH88" t="str">
             <v>D</v>
@@ -1804,16 +1806,16 @@
         </row>
         <row r="89">
           <cell r="AD89" t="str">
-            <v>壺壺</v>
+            <v>幾何雪花</v>
           </cell>
           <cell r="AE89" t="str">
-            <v>岩石</v>
+            <v>冰</v>
           </cell>
           <cell r="AF89" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG89">
-            <v>17</v>
+            <v>153</v>
           </cell>
           <cell r="AH89" t="str">
             <v>D</v>
@@ -1824,7 +1826,7 @@
             <v>壺壺</v>
           </cell>
           <cell r="AE90" t="str">
-            <v>蟲</v>
+            <v>岩石</v>
           </cell>
           <cell r="AF90" t="str">
             <v>Y</v>
@@ -1838,16 +1840,16 @@
         </row>
         <row r="91">
           <cell r="AD91" t="str">
-            <v>胡地</v>
+            <v>壺壺</v>
           </cell>
           <cell r="AE91" t="str">
-            <v>超能力</v>
+            <v>蟲</v>
           </cell>
           <cell r="AF91" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG91">
-            <v>225</v>
+            <v>17</v>
           </cell>
           <cell r="AH91" t="str">
             <v>D</v>
@@ -1858,10 +1860,10 @@
             <v>胡地</v>
           </cell>
           <cell r="AE92" t="str">
-            <v>格鬥</v>
+            <v>超能力</v>
           </cell>
           <cell r="AF92" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG92">
             <v>225</v>
@@ -1872,16 +1874,16 @@
         </row>
         <row r="93">
           <cell r="AD93" t="str">
-            <v>拉普拉斯</v>
+            <v>胡地</v>
           </cell>
           <cell r="AE93" t="str">
-            <v>冰</v>
+            <v>格鬥</v>
           </cell>
           <cell r="AF93" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG93">
-            <v>141</v>
+            <v>225</v>
           </cell>
           <cell r="AH93" t="str">
             <v>D</v>
@@ -1889,19 +1891,19 @@
         </row>
         <row r="94">
           <cell r="AD94" t="str">
-            <v>鋁鋼龍</v>
+            <v>超極巨拉普拉斯</v>
           </cell>
           <cell r="AE94" t="str">
-            <v>鋼</v>
+            <v>冰</v>
           </cell>
           <cell r="AF94" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG94">
-            <v>201</v>
+            <v>141</v>
           </cell>
           <cell r="AH94" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="95">
@@ -1909,7 +1911,7 @@
             <v>鋁鋼龍</v>
           </cell>
           <cell r="AE95" t="str">
-            <v>龍</v>
+            <v>鋼</v>
           </cell>
           <cell r="AF95" t="str">
             <v>Y</v>
@@ -1926,10 +1928,10 @@
             <v>鋁鋼龍</v>
           </cell>
           <cell r="AE96" t="str">
-            <v>一般</v>
+            <v>龍</v>
           </cell>
           <cell r="AF96" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG96">
             <v>201</v>
@@ -1940,16 +1942,16 @@
         </row>
         <row r="97">
           <cell r="AD97" t="str">
-            <v>巨金怪</v>
+            <v>鋁鋼龍</v>
           </cell>
           <cell r="AE97" t="str">
-            <v>幽靈</v>
+            <v>一般</v>
           </cell>
           <cell r="AF97" t="str">
             <v>N</v>
           </cell>
           <cell r="AG97">
-            <v>214</v>
+            <v>201</v>
           </cell>
           <cell r="AH97" t="str">
             <v>D</v>
@@ -1957,16 +1959,16 @@
         </row>
         <row r="98">
           <cell r="AD98" t="str">
-            <v>沙奈朵</v>
+            <v>巨金怪</v>
           </cell>
           <cell r="AE98" t="str">
-            <v>妖精</v>
+            <v>幽靈</v>
           </cell>
           <cell r="AF98" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG98">
-            <v>199</v>
+            <v>214</v>
           </cell>
           <cell r="AH98" t="str">
             <v>D</v>
@@ -1977,7 +1979,7 @@
             <v>沙奈朵</v>
           </cell>
           <cell r="AE99" t="str">
-            <v>超能力</v>
+            <v>妖精</v>
           </cell>
           <cell r="AF99" t="str">
             <v>Y</v>
@@ -1994,10 +1996,10 @@
             <v>沙奈朵</v>
           </cell>
           <cell r="AE100" t="str">
-            <v>草</v>
+            <v>超能力</v>
           </cell>
           <cell r="AF100" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG100">
             <v>199</v>
@@ -2011,7 +2013,7 @@
             <v>沙奈朵</v>
           </cell>
           <cell r="AE101" t="str">
-            <v>電</v>
+            <v>草</v>
           </cell>
           <cell r="AF101" t="str">
             <v>N</v>
@@ -2025,16 +2027,16 @@
         </row>
         <row r="102">
           <cell r="AD102" t="str">
-            <v>甜冷美后</v>
+            <v>沙奈朵</v>
           </cell>
           <cell r="AE102" t="str">
-            <v>草</v>
+            <v>電</v>
           </cell>
           <cell r="AF102" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG102">
-            <v>187</v>
+            <v>199</v>
           </cell>
           <cell r="AH102" t="str">
             <v>D</v>
@@ -2045,10 +2047,10 @@
             <v>甜冷美后</v>
           </cell>
           <cell r="AE103" t="str">
-            <v>妖精</v>
+            <v>草</v>
           </cell>
           <cell r="AF103" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG103">
             <v>187</v>
@@ -2059,50 +2061,50 @@
         </row>
         <row r="104">
           <cell r="AD104" t="str">
-            <v>超極巨伊布</v>
+            <v>甜冷美后</v>
           </cell>
           <cell r="AE104" t="str">
-            <v>一般</v>
+            <v>妖精</v>
           </cell>
           <cell r="AF104" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG104">
-            <v>94</v>
+            <v>187</v>
           </cell>
           <cell r="AH104" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="105">
           <cell r="AD105" t="str">
-            <v>水伊布</v>
+            <v>超極巨伊布</v>
           </cell>
           <cell r="AE105" t="str">
-            <v>水</v>
+            <v>一般</v>
           </cell>
           <cell r="AF105" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG105">
-            <v>174</v>
+            <v>94</v>
           </cell>
           <cell r="AH105" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="106">
           <cell r="AD106" t="str">
-            <v>雷伊布</v>
+            <v>水伊布</v>
           </cell>
           <cell r="AE106" t="str">
-            <v>電</v>
+            <v>水</v>
           </cell>
           <cell r="AF106" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG106">
-            <v>195</v>
+            <v>174</v>
           </cell>
           <cell r="AH106" t="str">
             <v>D</v>
@@ -2110,16 +2112,16 @@
         </row>
         <row r="107">
           <cell r="AD107" t="str">
-            <v>火伊布</v>
+            <v>雷伊布</v>
           </cell>
           <cell r="AE107" t="str">
-            <v>火</v>
+            <v>電</v>
           </cell>
           <cell r="AF107" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG107">
-            <v>206</v>
+            <v>195</v>
           </cell>
           <cell r="AH107" t="str">
             <v>D</v>
@@ -2127,16 +2129,16 @@
         </row>
         <row r="108">
           <cell r="AD108" t="str">
-            <v>太陽伊布</v>
+            <v>火伊布</v>
           </cell>
           <cell r="AE108" t="str">
-            <v>超能力</v>
+            <v>火</v>
           </cell>
           <cell r="AF108" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG108">
-            <v>218</v>
+            <v>206</v>
           </cell>
           <cell r="AH108" t="str">
             <v>D</v>
@@ -2144,16 +2146,16 @@
         </row>
         <row r="109">
           <cell r="AD109" t="str">
-            <v>月亮伊布</v>
+            <v>太陽伊布</v>
           </cell>
           <cell r="AE109" t="str">
-            <v>惡</v>
+            <v>超能力</v>
           </cell>
           <cell r="AF109" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG109">
-            <v>111</v>
+            <v>218</v>
           </cell>
           <cell r="AH109" t="str">
             <v>D</v>
@@ -2161,16 +2163,16 @@
         </row>
         <row r="110">
           <cell r="AD110" t="str">
-            <v>葉伊布</v>
+            <v>月亮伊布</v>
           </cell>
           <cell r="AE110" t="str">
-            <v>草</v>
+            <v>惡</v>
           </cell>
           <cell r="AF110" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG110">
-            <v>183</v>
+            <v>111</v>
           </cell>
           <cell r="AH110" t="str">
             <v>D</v>
@@ -2178,16 +2180,16 @@
         </row>
         <row r="111">
           <cell r="AD111" t="str">
-            <v>冰伊布</v>
+            <v>葉伊布</v>
           </cell>
           <cell r="AE111" t="str">
-            <v>冰</v>
+            <v>草</v>
           </cell>
           <cell r="AF111" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG111">
-            <v>200</v>
+            <v>183</v>
           </cell>
           <cell r="AH111" t="str">
             <v>D</v>
@@ -2195,16 +2197,16 @@
         </row>
         <row r="112">
           <cell r="AD112" t="str">
-            <v>仙子伊布</v>
+            <v>冰伊布</v>
           </cell>
           <cell r="AE112" t="str">
-            <v>妖精</v>
+            <v>冰</v>
           </cell>
           <cell r="AF112" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG112">
-            <v>172</v>
+            <v>200</v>
           </cell>
           <cell r="AH112" t="str">
             <v>D</v>
@@ -2212,16 +2214,16 @@
         </row>
         <row r="113">
           <cell r="AD113" t="str">
-            <v>艾路雷朵</v>
+            <v>仙子伊布</v>
           </cell>
           <cell r="AE113" t="str">
-            <v>格鬥</v>
+            <v>妖精</v>
           </cell>
           <cell r="AF113" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG113">
-            <v>199</v>
+            <v>172</v>
           </cell>
           <cell r="AH113" t="str">
             <v>D</v>
@@ -2232,7 +2234,7 @@
             <v>艾路雷朵</v>
           </cell>
           <cell r="AE114" t="str">
-            <v>超能力</v>
+            <v>格鬥</v>
           </cell>
           <cell r="AF114" t="str">
             <v>Y</v>
@@ -2249,10 +2251,10 @@
             <v>艾路雷朵</v>
           </cell>
           <cell r="AE115" t="str">
-            <v>妖精</v>
+            <v>超能力</v>
           </cell>
           <cell r="AF115" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG115">
             <v>199</v>
@@ -2263,16 +2265,16 @@
         </row>
         <row r="116">
           <cell r="AD116" t="str">
-            <v>烏賊王</v>
+            <v>艾路雷朵</v>
           </cell>
           <cell r="AE116" t="str">
-            <v>超能力</v>
+            <v>妖精</v>
           </cell>
           <cell r="AF116" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG116">
-            <v>151</v>
+            <v>199</v>
           </cell>
           <cell r="AH116" t="str">
             <v>D</v>
@@ -2283,10 +2285,10 @@
             <v>烏賊王</v>
           </cell>
           <cell r="AE117" t="str">
-            <v>飛行</v>
+            <v>超能力</v>
           </cell>
           <cell r="AF117" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG117">
             <v>151</v>
@@ -2297,16 +2299,16 @@
         </row>
         <row r="118">
           <cell r="AD118" t="str">
-            <v>洛奇亞</v>
+            <v>烏賊王</v>
           </cell>
           <cell r="AE118" t="str">
-            <v>超能力</v>
+            <v>飛行</v>
           </cell>
           <cell r="AF118" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG118">
-            <v>164</v>
+            <v>151</v>
           </cell>
           <cell r="AH118" t="str">
             <v>D</v>
@@ -2317,10 +2319,10 @@
             <v>洛奇亞</v>
           </cell>
           <cell r="AE119" t="str">
-            <v>龍</v>
+            <v>超能力</v>
           </cell>
           <cell r="AF119" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG119">
             <v>164</v>
@@ -2331,16 +2333,16 @@
         </row>
         <row r="120">
           <cell r="AD120" t="str">
-            <v>飛腿郎</v>
+            <v>洛奇亞</v>
           </cell>
           <cell r="AE120" t="str">
-            <v>格鬥</v>
+            <v>龍</v>
           </cell>
           <cell r="AF120" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG120">
-            <v>189</v>
+            <v>164</v>
           </cell>
           <cell r="AH120" t="str">
             <v>D</v>
@@ -2348,7 +2350,7 @@
         </row>
         <row r="121">
           <cell r="AD121" t="str">
-            <v>快拳郎</v>
+            <v>飛腿郎</v>
           </cell>
           <cell r="AE121" t="str">
             <v>格鬥</v>
@@ -2357,7 +2359,7 @@
             <v>Y</v>
           </cell>
           <cell r="AG121">
-            <v>164</v>
+            <v>189</v>
           </cell>
           <cell r="AH121" t="str">
             <v>D</v>
@@ -2368,10 +2370,10 @@
             <v>快拳郎</v>
           </cell>
           <cell r="AE122" t="str">
-            <v>鋼</v>
+            <v>格鬥</v>
           </cell>
           <cell r="AF122" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG122">
             <v>164</v>
@@ -2382,16 +2384,16 @@
         </row>
         <row r="123">
           <cell r="AD123" t="str">
-            <v>帝牙海獅</v>
+            <v>快拳郎</v>
           </cell>
           <cell r="AE123" t="str">
-            <v>水</v>
+            <v>鋼</v>
           </cell>
           <cell r="AF123" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AG123">
-            <v>156</v>
+            <v>164</v>
           </cell>
           <cell r="AH123" t="str">
             <v>D</v>
@@ -2402,7 +2404,7 @@
             <v>帝牙海獅</v>
           </cell>
           <cell r="AE124" t="str">
-            <v>冰</v>
+            <v>水</v>
           </cell>
           <cell r="AF124" t="str">
             <v>Y</v>
@@ -2416,16 +2418,16 @@
         </row>
         <row r="125">
           <cell r="AD125" t="str">
-            <v>龐岩怪</v>
+            <v>帝牙海獅</v>
           </cell>
           <cell r="AE125" t="str">
-            <v>岩石</v>
+            <v>冰</v>
           </cell>
           <cell r="AF125" t="str">
             <v>Y</v>
           </cell>
           <cell r="AG125">
-            <v>190</v>
+            <v>156</v>
           </cell>
           <cell r="AH125" t="str">
             <v>D</v>
@@ -2433,16 +2435,16 @@
         </row>
         <row r="129">
           <cell r="AD129" t="str">
-            <v>鳳王</v>
+            <v>老翁龍</v>
           </cell>
           <cell r="AE129" t="str">
-            <v>火</v>
+            <v>一般</v>
           </cell>
           <cell r="AF129" t="str">
             <v>N</v>
           </cell>
           <cell r="AG129">
-            <v>201</v>
+            <v>194</v>
           </cell>
           <cell r="AH129" t="str">
             <v>D</v>
@@ -2453,10 +2455,10 @@
             <v>鳳王</v>
           </cell>
           <cell r="AE130" t="str">
-            <v>超能力</v>
+            <v>火</v>
           </cell>
           <cell r="AF130" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AG130">
             <v>201</v>
@@ -2470,7 +2472,7 @@
             <v>鳳王</v>
           </cell>
           <cell r="AE131" t="str">
-            <v>一般</v>
+            <v>超能力</v>
           </cell>
           <cell r="AF131" t="str">
             <v>N</v>
@@ -2487,7 +2489,7 @@
             <v>鳳王</v>
           </cell>
           <cell r="AE132" t="str">
-            <v>鋼</v>
+            <v>一般</v>
           </cell>
           <cell r="AF132" t="str">
             <v>N</v>
@@ -2496,6 +2498,278 @@
             <v>201</v>
           </cell>
           <cell r="AH132" t="str">
+            <v>D</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="AD133" t="str">
+            <v>鳳王</v>
+          </cell>
+          <cell r="AE133" t="str">
+            <v>鋼</v>
+          </cell>
+          <cell r="AF133" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="AG133">
+            <v>201</v>
+          </cell>
+          <cell r="AH133" t="str">
+            <v>D</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="AD134" t="str">
+            <v>風速狗</v>
+          </cell>
+          <cell r="AE134" t="str">
+            <v>火</v>
+          </cell>
+          <cell r="AF134" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AG134">
+            <v>191</v>
+          </cell>
+          <cell r="AH134" t="str">
+            <v>D</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="AD135" t="str">
+            <v>風速狗</v>
+          </cell>
+          <cell r="AE135" t="str">
+            <v>惡</v>
+          </cell>
+          <cell r="AF135" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="AG135">
+            <v>191</v>
+          </cell>
+          <cell r="AH135" t="str">
+            <v>D</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="AD136" t="str">
+            <v>風速狗</v>
+          </cell>
+          <cell r="AE136" t="str">
+            <v>電</v>
+          </cell>
+          <cell r="AF136" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="AG136">
+            <v>191</v>
+          </cell>
+          <cell r="AH136" t="str">
+            <v>D</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="AD137" t="str">
+            <v>固拉多</v>
+          </cell>
+          <cell r="AE137" t="str">
+            <v>地面</v>
+          </cell>
+          <cell r="AF137" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AG137">
+            <v>225</v>
+          </cell>
+          <cell r="AH137" t="str">
+            <v>D</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="AD138" t="str">
+            <v>固拉多</v>
+          </cell>
+          <cell r="AE138" t="str">
+            <v>龍</v>
+          </cell>
+          <cell r="AF138" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AG138">
+            <v>225</v>
+          </cell>
+          <cell r="AH138" t="str">
+            <v>D</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="AD139" t="str">
+            <v>蓋歐卡</v>
+          </cell>
+          <cell r="AE139" t="str">
+            <v>水</v>
+          </cell>
+          <cell r="AF139" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AG139">
+            <v>225</v>
+          </cell>
+          <cell r="AH139" t="str">
+            <v>D</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="AD140" t="str">
+            <v>烈空坐</v>
+          </cell>
+          <cell r="AE140" t="str">
+            <v>龍</v>
+          </cell>
+          <cell r="AF140" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AG140">
+            <v>236</v>
+          </cell>
+          <cell r="AH140" t="str">
+            <v>D</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="AD141" t="str">
+            <v>烈空坐</v>
+          </cell>
+          <cell r="AE141" t="str">
+            <v>飛行</v>
+          </cell>
+          <cell r="AF141" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AG141">
+            <v>236</v>
+          </cell>
+          <cell r="AH141" t="str">
+            <v>D</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="AD142" t="str">
+            <v>喵喵</v>
+          </cell>
+          <cell r="AE142" t="str">
+            <v>一般</v>
+          </cell>
+          <cell r="AF142" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AG142">
+            <v>85</v>
+          </cell>
+          <cell r="AH142" t="str">
+            <v>G</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="AD143" t="str">
+            <v>皮卡丘</v>
+          </cell>
+          <cell r="AE143" t="str">
+            <v>電</v>
+          </cell>
+          <cell r="AF143" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AG143">
+            <v>100</v>
+          </cell>
+          <cell r="AH143" t="str">
+            <v>G</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="AD144" t="str">
+            <v>雷丘</v>
+          </cell>
+          <cell r="AE144" t="str">
+            <v>電</v>
+          </cell>
+          <cell r="AF144" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AG144">
+            <v>164</v>
+          </cell>
+          <cell r="AH144" t="str">
+            <v>D</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="AD145" t="str">
+            <v>雷丘</v>
+          </cell>
+          <cell r="AE145" t="str">
+            <v>妖精</v>
+          </cell>
+          <cell r="AF145" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="AG145">
+            <v>164</v>
+          </cell>
+          <cell r="AH145" t="str">
+            <v>D</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="AD146" t="str">
+            <v>雷吉艾斯</v>
+          </cell>
+          <cell r="AE146" t="str">
+            <v>冰</v>
+          </cell>
+          <cell r="AF146" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AG146">
+            <v>153</v>
+          </cell>
+          <cell r="AH146" t="str">
+            <v>D</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="AD147" t="str">
+            <v>雷吉艾斯</v>
+          </cell>
+          <cell r="AE147" t="str">
+            <v>一般</v>
+          </cell>
+          <cell r="AF147" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="AG147">
+            <v>153</v>
+          </cell>
+          <cell r="AH147" t="str">
+            <v>D</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="AD148" t="str">
+            <v>雷吉艾斯</v>
+          </cell>
+          <cell r="AE148" t="str">
+            <v>格鬥</v>
+          </cell>
+          <cell r="AF148" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="AG148">
+            <v>153</v>
+          </cell>
+          <cell r="AH148" t="str">
             <v>D</v>
           </cell>
         </row>
@@ -2505,6 +2779,7 @@
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2774,11 +3049,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AB150"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:28" x14ac:dyDescent="0.3">
@@ -2863,7 +3138,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="2:28" ht="17" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="str">
         <f>[1]攻守數據!AD3</f>
         <v>超極巨轟擂金剛猩</v>
@@ -3027,7 +3302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:28" ht="17" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="str">
         <f>[1]攻守數據!AD5</f>
         <v>超極巨怪力</v>
@@ -3276,11 +3551,11 @@
     <row r="7" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="str">
         <f>[1]攻守數據!AD8</f>
-        <v>超極巨顫弦蠑螈</v>
+        <v>卡比獸</v>
       </c>
       <c r="C7" s="1" t="str">
         <f>[1]攻守數據!AE8</f>
-        <v>電</v>
+        <v>一般</v>
       </c>
       <c r="D7" s="1" t="str">
         <f>[1]攻守數據!AF8</f>
@@ -3288,7 +3563,7 @@
       </c>
       <c r="E7" s="1">
         <f>[1]攻守數據!AG8</f>
-        <v>188</v>
+        <v>149</v>
       </c>
       <c r="F7" s="1" t="str">
         <f>[1]攻守數據!AH8</f>
@@ -3355,10 +3630,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:28" ht="17" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="str">
         <f>[1]攻守數據!AD9</f>
-        <v>顫弦蠑螈</v>
+        <v>超極巨顫弦蠑螈</v>
       </c>
       <c r="C8" s="1" t="str">
         <f>[1]攻守數據!AE9</f>
@@ -3374,7 +3649,7 @@
       </c>
       <c r="F8" s="1" t="str">
         <f>[1]攻守數據!AH9</f>
-        <v>D</v>
+        <v>G</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>10</v>
@@ -3437,14 +3712,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:28" ht="17" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="str">
         <f>[1]攻守數據!AD10</f>
         <v>顫弦蠑螈</v>
       </c>
       <c r="C9" s="1" t="str">
         <f>[1]攻守數據!AE10</f>
-        <v>毒</v>
+        <v>電</v>
       </c>
       <c r="D9" s="1" t="str">
         <f>[1]攻守數據!AF10</f>
@@ -3519,14 +3794,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:28" ht="17" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="str">
         <f>[1]攻守數據!AD11</f>
-        <v>超極巨妙蛙花</v>
+        <v>顫弦蠑螈</v>
       </c>
       <c r="C10" s="1" t="str">
         <f>[1]攻守數據!AE11</f>
-        <v>草</v>
+        <v>毒</v>
       </c>
       <c r="D10" s="1" t="str">
         <f>[1]攻守數據!AF11</f>
@@ -3534,11 +3809,11 @@
       </c>
       <c r="E10" s="1">
         <f>[1]攻守數據!AG11</f>
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="F10" s="1" t="str">
         <f>[1]攻守數據!AH11</f>
-        <v>G</v>
+        <v>D</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>18</v>
@@ -3601,10 +3876,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:28" ht="17" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="str">
         <f>[1]攻守數據!AD12</f>
-        <v>妙蛙花</v>
+        <v>超極巨妙蛙花</v>
       </c>
       <c r="C11" s="1" t="str">
         <f>[1]攻守數據!AE12</f>
@@ -3620,7 +3895,7 @@
       </c>
       <c r="F11" s="1" t="str">
         <f>[1]攻守數據!AH12</f>
-        <v>D</v>
+        <v>G</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>14</v>
@@ -3686,11 +3961,11 @@
     <row r="12" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="str">
         <f>[1]攻守數據!AD13</f>
-        <v>武道熊師(一)</v>
+        <v>妙蛙花</v>
       </c>
       <c r="C12" s="1" t="str">
         <f>[1]攻守數據!AE13</f>
-        <v>格鬥</v>
+        <v>草</v>
       </c>
       <c r="D12" s="1" t="str">
         <f>[1]攻守數據!AF13</f>
@@ -3698,7 +3973,7 @@
       </c>
       <c r="E12" s="1">
         <f>[1]攻守數據!AG13</f>
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="F12" s="1" t="str">
         <f>[1]攻守數據!AH13</f>
@@ -3768,11 +4043,11 @@
     <row r="13" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="str">
         <f>[1]攻守數據!AD14</f>
-        <v>武道熊師(連)</v>
+        <v>武道熊師(一)</v>
       </c>
       <c r="C13" s="1" t="str">
         <f>[1]攻守數據!AE14</f>
-        <v>水</v>
+        <v>格鬥</v>
       </c>
       <c r="D13" s="1" t="str">
         <f>[1]攻守數據!AF14</f>
@@ -3850,11 +4125,11 @@
     <row r="14" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="str">
         <f>[1]攻守數據!AD15</f>
-        <v>閃電鳥</v>
+        <v>武道熊師(連)</v>
       </c>
       <c r="C14" s="1" t="str">
         <f>[1]攻守數據!AE15</f>
-        <v>電</v>
+        <v>水</v>
       </c>
       <c r="D14" s="1" t="str">
         <f>[1]攻守數據!AF15</f>
@@ -3862,7 +4137,7 @@
       </c>
       <c r="E14" s="1">
         <f>[1]攻守數據!AG15</f>
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F14" s="1" t="str">
         <f>[1]攻守數據!AH15</f>
@@ -3929,10 +4204,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:28" ht="17" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="str">
         <f>[1]攻守數據!AD16</f>
-        <v>雷公</v>
+        <v>閃電鳥</v>
       </c>
       <c r="C15" s="1" t="str">
         <f>[1]攻守數據!AE16</f>
@@ -3944,7 +4219,7 @@
       </c>
       <c r="E15" s="1">
         <f>[1]攻守數據!AG16</f>
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F15" s="1" t="str">
         <f>[1]攻守數據!AH16</f>
@@ -4011,14 +4286,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:28" ht="17" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="str">
         <f>[1]攻守數據!AD17</f>
-        <v>投擲猴</v>
+        <v>雷公</v>
       </c>
       <c r="C16" s="1" t="str">
         <f>[1]攻守數據!AE17</f>
-        <v>格鬥</v>
+        <v>電</v>
       </c>
       <c r="D16" s="1" t="str">
         <f>[1]攻守數據!AF17</f>
@@ -4026,7 +4301,7 @@
       </c>
       <c r="E16" s="1">
         <f>[1]攻守數據!AG17</f>
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="F16" s="1" t="str">
         <f>[1]攻守數據!AH17</f>
@@ -4096,11 +4371,11 @@
     <row r="17" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="str">
         <f>[1]攻守數據!AD18</f>
-        <v>超極巨耿鬼</v>
+        <v>投擲猴</v>
       </c>
       <c r="C17" s="1" t="str">
         <f>[1]攻守數據!AE18</f>
-        <v>幽靈</v>
+        <v>格鬥</v>
       </c>
       <c r="D17" s="1" t="str">
         <f>[1]攻守數據!AF18</f>
@@ -4108,11 +4383,11 @@
       </c>
       <c r="E17" s="1">
         <f>[1]攻守數據!AG18</f>
-        <v>223</v>
+        <v>181</v>
       </c>
       <c r="F17" s="1" t="str">
         <f>[1]攻守數據!AH18</f>
-        <v>G</v>
+        <v>D</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>7</v>
@@ -4178,15 +4453,15 @@
     <row r="18" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="str">
         <f>[1]攻守數據!AD19</f>
-        <v>耿鬼</v>
+        <v>超極巨耿鬼</v>
       </c>
       <c r="C18" s="1" t="str">
         <f>[1]攻守數據!AE19</f>
-        <v>惡</v>
+        <v>幽靈</v>
       </c>
       <c r="D18" s="1" t="str">
         <f>[1]攻守數據!AF19</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E18" s="1">
         <f>[1]攻守數據!AG19</f>
@@ -4194,7 +4469,7 @@
       </c>
       <c r="F18" s="1" t="str">
         <f>[1]攻守數據!AH19</f>
-        <v>D</v>
+        <v>G</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>4</v>
@@ -4264,11 +4539,11 @@
       </c>
       <c r="C19" s="1" t="str">
         <f>[1]攻守數據!AE20</f>
-        <v>幽靈</v>
+        <v>惡</v>
       </c>
       <c r="D19" s="1" t="str">
         <f>[1]攻守數據!AF20</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E19" s="1">
         <f>[1]攻守數據!AG20</f>
@@ -4342,11 +4617,11 @@
     <row r="20" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="str">
         <f>[1]攻守數據!AD21</f>
-        <v>蒼響</v>
+        <v>耿鬼</v>
       </c>
       <c r="C20" s="1" t="str">
         <f>[1]攻守數據!AE21</f>
-        <v>鋼</v>
+        <v>幽靈</v>
       </c>
       <c r="D20" s="1" t="str">
         <f>[1]攻守數據!AF21</f>
@@ -4354,7 +4629,7 @@
       </c>
       <c r="E20" s="1">
         <f>[1]攻守數據!AG21</f>
-        <v>291</v>
+        <v>223</v>
       </c>
       <c r="F20" s="1" t="str">
         <f>[1]攻守數據!AH21</f>
@@ -4424,11 +4699,11 @@
     <row r="21" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="str">
         <f>[1]攻守數據!AD22</f>
-        <v>多刺菊石獸</v>
+        <v>蒼響</v>
       </c>
       <c r="C21" s="1" t="str">
         <f>[1]攻守數據!AE22</f>
-        <v>岩石</v>
+        <v>鋼</v>
       </c>
       <c r="D21" s="1" t="str">
         <f>[1]攻守數據!AF22</f>
@@ -4436,7 +4711,7 @@
       </c>
       <c r="E21" s="1">
         <f>[1]攻守數據!AG22</f>
-        <v>177</v>
+        <v>291</v>
       </c>
       <c r="F21" s="1" t="str">
         <f>[1]攻守數據!AH22</f>
@@ -4446,11 +4721,11 @@
     <row r="22" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="str">
         <f>[1]攻守數據!AD23</f>
-        <v>妙蛙花</v>
+        <v>多刺菊石獸</v>
       </c>
       <c r="C22" s="1" t="str">
         <f>[1]攻守數據!AE23</f>
-        <v>草</v>
+        <v>岩石</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>[1]攻守數據!AF23</f>
@@ -4458,7 +4733,7 @@
       </c>
       <c r="E22" s="1">
         <f>[1]攻守數據!AG23</f>
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="F22" s="1" t="str">
         <f>[1]攻守數據!AH23</f>
@@ -4468,11 +4743,11 @@
     <row r="23" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="str">
         <f>[1]攻守數據!AD24</f>
-        <v>列陣兵</v>
+        <v>妙蛙花</v>
       </c>
       <c r="C23" s="1" t="str">
         <f>[1]攻守數據!AE24</f>
-        <v>格鬥</v>
+        <v>草</v>
       </c>
       <c r="D23" s="1" t="str">
         <f>[1]攻守數據!AF24</f>
@@ -4480,7 +4755,7 @@
       </c>
       <c r="E23" s="1">
         <f>[1]攻守數據!AG24</f>
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F23" s="1" t="str">
         <f>[1]攻守數據!AH24</f>
@@ -4490,11 +4765,11 @@
     <row r="24" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="str">
         <f>[1]攻守數據!AD25</f>
-        <v>超極巨閃焰王牌</v>
+        <v>列陣兵</v>
       </c>
       <c r="C24" s="1" t="str">
         <f>[1]攻守數據!AE25</f>
-        <v>火</v>
+        <v>格鬥</v>
       </c>
       <c r="D24" s="1" t="str">
         <f>[1]攻守數據!AF25</f>
@@ -4502,17 +4777,17 @@
       </c>
       <c r="E24" s="1">
         <f>[1]攻守數據!AG25</f>
-        <v>205</v>
+        <v>160</v>
       </c>
       <c r="F24" s="1" t="str">
         <f>[1]攻守數據!AH25</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="str">
         <f>[1]攻守數據!AD26</f>
-        <v>閃焰王牌</v>
+        <v>超極巨閃焰王牌</v>
       </c>
       <c r="C25" s="1" t="str">
         <f>[1]攻守數據!AE26</f>
@@ -4528,25 +4803,25 @@
       </c>
       <c r="F25" s="1" t="str">
         <f>[1]攻守數據!AH26</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="str">
         <f>[1]攻守數據!AD27</f>
-        <v>鐮刀盔</v>
+        <v>閃焰王牌</v>
       </c>
       <c r="C26" s="1" t="str">
         <f>[1]攻守數據!AE27</f>
-        <v>格鬥</v>
+        <v>火</v>
       </c>
       <c r="D26" s="1" t="str">
         <f>[1]攻守數據!AF27</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E26" s="1">
         <f>[1]攻守數據!AG27</f>
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="F26" s="1" t="str">
         <f>[1]攻守數據!AH27</f>
@@ -4556,33 +4831,33 @@
     <row r="27" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="str">
         <f>[1]攻守數據!AD28</f>
-        <v>超極巨噴火龍</v>
+        <v>鐮刀盔</v>
       </c>
       <c r="C27" s="1" t="str">
         <f>[1]攻守數據!AE28</f>
-        <v>火</v>
+        <v>格鬥</v>
       </c>
       <c r="D27" s="1" t="str">
         <f>[1]攻守數據!AF28</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E27" s="1">
         <f>[1]攻守數據!AG28</f>
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F27" s="1" t="str">
         <f>[1]攻守數據!AH28</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="28" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="str">
         <f>[1]攻守數據!AD29</f>
-        <v>噴火龍</v>
+        <v>超極巨噴火龍</v>
       </c>
       <c r="C28" s="1" t="str">
         <f>[1]攻守數據!AE29</f>
-        <v>飛行</v>
+        <v>火</v>
       </c>
       <c r="D28" s="1" t="str">
         <f>[1]攻守數據!AF29</f>
@@ -4594,7 +4869,7 @@
       </c>
       <c r="F28" s="1" t="str">
         <f>[1]攻守數據!AH29</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.3">
@@ -4604,7 +4879,7 @@
       </c>
       <c r="C29" s="1" t="str">
         <f>[1]攻守數據!AE30</f>
-        <v>火</v>
+        <v>飛行</v>
       </c>
       <c r="D29" s="1" t="str">
         <f>[1]攻守數據!AF30</f>
@@ -4626,11 +4901,11 @@
       </c>
       <c r="C30" s="1" t="str">
         <f>[1]攻守數據!AE31</f>
-        <v>龍</v>
+        <v>火</v>
       </c>
       <c r="D30" s="1" t="str">
         <f>[1]攻守數據!AF31</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E30" s="1">
         <f>[1]攻守數據!AG31</f>
@@ -4644,7 +4919,7 @@
     <row r="31" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="str">
         <f>[1]攻守數據!AD32</f>
-        <v>無極汰那</v>
+        <v>噴火龍</v>
       </c>
       <c r="C31" s="1" t="str">
         <f>[1]攻守數據!AE32</f>
@@ -4652,25 +4927,25 @@
       </c>
       <c r="D31" s="1" t="str">
         <f>[1]攻守數據!AF32</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E31" s="1">
         <f>[1]攻守數據!AG32</f>
-        <v>231</v>
+        <v>187</v>
       </c>
       <c r="F31" s="1" t="str">
         <f>[1]攻守數據!AH32</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="32" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="str">
         <f>[1]攻守數據!AD33</f>
-        <v>拉帝歐斯</v>
+        <v>無極汰那</v>
       </c>
       <c r="C32" s="1" t="str">
         <f>[1]攻守數據!AE33</f>
-        <v>超能力</v>
+        <v>龍</v>
       </c>
       <c r="D32" s="1" t="str">
         <f>[1]攻守數據!AF33</f>
@@ -4678,11 +4953,11 @@
       </c>
       <c r="E32" s="1">
         <f>[1]攻守數據!AG33</f>
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="F32" s="1" t="str">
         <f>[1]攻守數據!AH33</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
@@ -4692,7 +4967,7 @@
       </c>
       <c r="C33" s="1" t="str">
         <f>[1]攻守數據!AE34</f>
-        <v>龍</v>
+        <v>超能力</v>
       </c>
       <c r="D33" s="1" t="str">
         <f>[1]攻守數據!AF34</f>
@@ -4710,11 +4985,11 @@
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="str">
         <f>[1]攻守數據!AD35</f>
-        <v>狒狒達摩</v>
+        <v>拉帝歐斯</v>
       </c>
       <c r="C34" s="1" t="str">
         <f>[1]攻守數據!AE35</f>
-        <v>火</v>
+        <v>龍</v>
       </c>
       <c r="D34" s="1" t="str">
         <f>[1]攻守數據!AF35</f>
@@ -4722,7 +4997,7 @@
       </c>
       <c r="E34" s="1">
         <f>[1]攻守數據!AG35</f>
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F34" s="1" t="str">
         <f>[1]攻守數據!AH35</f>
@@ -4732,11 +5007,11 @@
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="str">
         <f>[1]攻守數據!AD36</f>
-        <v>巨金怪</v>
+        <v>狒狒達摩</v>
       </c>
       <c r="C35" s="1" t="str">
         <f>[1]攻守數據!AE36</f>
-        <v>超能力</v>
+        <v>火</v>
       </c>
       <c r="D35" s="1" t="str">
         <f>[1]攻守數據!AF36</f>
@@ -4744,7 +5019,7 @@
       </c>
       <c r="E35" s="1">
         <f>[1]攻守數據!AG36</f>
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F35" s="1" t="str">
         <f>[1]攻守數據!AH36</f>
@@ -4758,7 +5033,7 @@
       </c>
       <c r="C36" s="1" t="str">
         <f>[1]攻守數據!AE37</f>
-        <v>鋼</v>
+        <v>超能力</v>
       </c>
       <c r="D36" s="1" t="str">
         <f>[1]攻守數據!AF37</f>
@@ -4780,11 +5055,11 @@
       </c>
       <c r="C37" s="1" t="str">
         <f>[1]攻守數據!AE38</f>
-        <v>蟲</v>
+        <v>鋼</v>
       </c>
       <c r="D37" s="1" t="str">
         <f>[1]攻守數據!AF38</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E37" s="1">
         <f>[1]攻守數據!AG38</f>
@@ -4798,19 +5073,19 @@
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="str">
         <f>[1]攻守數據!AD39</f>
-        <v>龍頭地鼠</v>
+        <v>巨金怪</v>
       </c>
       <c r="C38" s="1" t="str">
         <f>[1]攻守數據!AE39</f>
-        <v>地面</v>
+        <v>蟲</v>
       </c>
       <c r="D38" s="1" t="str">
         <f>[1]攻守數據!AF39</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E38" s="1">
         <f>[1]攻守數據!AG39</f>
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F38" s="1" t="str">
         <f>[1]攻守數據!AH39</f>
@@ -4824,7 +5099,7 @@
       </c>
       <c r="C39" s="1" t="str">
         <f>[1]攻守數據!AE40</f>
-        <v>鋼</v>
+        <v>地面</v>
       </c>
       <c r="D39" s="1" t="str">
         <f>[1]攻守數據!AF40</f>
@@ -4832,7 +5107,7 @@
       </c>
       <c r="E39" s="1">
         <f>[1]攻守數據!AG40</f>
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F39" s="1" t="str">
         <f>[1]攻守數據!AH40</f>
@@ -4842,11 +5117,11 @@
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="str">
         <f>[1]攻守數據!AD41</f>
-        <v>武道熊師(一)</v>
+        <v>龍頭地鼠</v>
       </c>
       <c r="C40" s="1" t="str">
         <f>[1]攻守數據!AE41</f>
-        <v>惡</v>
+        <v>鋼</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>[1]攻守數據!AF41</f>
@@ -4854,7 +5129,7 @@
       </c>
       <c r="E40" s="1">
         <f>[1]攻守數據!AG41</f>
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="F40" s="1" t="str">
         <f>[1]攻守數據!AH41</f>
@@ -4864,11 +5139,11 @@
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="str">
         <f>[1]攻守數據!AD42</f>
-        <v>閃電鳥</v>
+        <v>武道熊師(一)</v>
       </c>
       <c r="C41" s="1" t="str">
         <f>[1]攻守數據!AE42</f>
-        <v>飛行</v>
+        <v>惡</v>
       </c>
       <c r="D41" s="1" t="str">
         <f>[1]攻守數據!AF42</f>
@@ -4876,7 +5151,7 @@
       </c>
       <c r="E41" s="1">
         <f>[1]攻守數據!AG42</f>
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F41" s="1" t="str">
         <f>[1]攻守數據!AH42</f>
@@ -4886,7 +5161,7 @@
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="str">
         <f>[1]攻守數據!AD43</f>
-        <v>火焰鳥</v>
+        <v>閃電鳥</v>
       </c>
       <c r="C42" s="1" t="str">
         <f>[1]攻守數據!AE43</f>
@@ -4898,7 +5173,7 @@
       </c>
       <c r="E42" s="1">
         <f>[1]攻守數據!AG43</f>
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F42" s="1" t="str">
         <f>[1]攻守數據!AH43</f>
@@ -4912,7 +5187,7 @@
       </c>
       <c r="C43" s="1" t="str">
         <f>[1]攻守數據!AE44</f>
-        <v>火</v>
+        <v>飛行</v>
       </c>
       <c r="D43" s="1" t="str">
         <f>[1]攻守數據!AF44</f>
@@ -4930,11 +5205,11 @@
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="str">
         <f>[1]攻守數據!AD45</f>
-        <v>藏瑪然特</v>
+        <v>火焰鳥</v>
       </c>
       <c r="C44" s="1" t="str">
         <f>[1]攻守數據!AE45</f>
-        <v>鋼</v>
+        <v>火</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>[1]攻守數據!AF45</f>
@@ -4942,7 +5217,7 @@
       </c>
       <c r="E44" s="1">
         <f>[1]攻守數據!AG45</f>
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="F44" s="1" t="str">
         <f>[1]攻守數據!AH45</f>
@@ -4952,11 +5227,11 @@
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="str">
         <f>[1]攻守數據!AD46</f>
-        <v>炎帝</v>
+        <v>藏瑪然特</v>
       </c>
       <c r="C45" s="1" t="str">
         <f>[1]攻守數據!AE46</f>
-        <v>火</v>
+        <v>鋼</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>[1]攻守數據!AF46</f>
@@ -4964,7 +5239,7 @@
       </c>
       <c r="E45" s="1">
         <f>[1]攻守數據!AG46</f>
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="F45" s="1" t="str">
         <f>[1]攻守數據!AH46</f>
@@ -4974,11 +5249,11 @@
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="str">
         <f>[1]攻守數據!AD47</f>
-        <v>布莉姆溫</v>
+        <v>炎帝</v>
       </c>
       <c r="C46" s="1" t="str">
         <f>[1]攻守數據!AE47</f>
-        <v>超能力</v>
+        <v>火</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>[1]攻守數據!AF47</f>
@@ -4986,7 +5261,7 @@
       </c>
       <c r="E46" s="1">
         <f>[1]攻守數據!AG47</f>
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="F46" s="1" t="str">
         <f>[1]攻守數據!AH47</f>
@@ -5000,7 +5275,7 @@
       </c>
       <c r="C47" s="1" t="str">
         <f>[1]攻守數據!AE48</f>
-        <v>妖精</v>
+        <v>超能力</v>
       </c>
       <c r="D47" s="1" t="str">
         <f>[1]攻守數據!AF48</f>
@@ -5018,19 +5293,19 @@
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="str">
         <f>[1]攻守數據!AD49</f>
-        <v>吼鯨王</v>
+        <v>布莉姆溫</v>
       </c>
       <c r="C48" s="1" t="str">
         <f>[1]攻守數據!AE49</f>
-        <v>岩石</v>
+        <v>妖精</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>[1]攻守數據!AF49</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E48" s="1">
         <f>[1]攻守數據!AG49</f>
-        <v>147</v>
+        <v>198</v>
       </c>
       <c r="F48" s="1" t="str">
         <f>[1]攻守數據!AH49</f>
@@ -5040,19 +5315,19 @@
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="str">
         <f>[1]攻守數據!AD50</f>
-        <v>拉帝亞斯</v>
+        <v>吼鯨王</v>
       </c>
       <c r="C49" s="1" t="str">
         <f>[1]攻守數據!AE50</f>
-        <v>超能力</v>
+        <v>岩石</v>
       </c>
       <c r="D49" s="1" t="str">
         <f>[1]攻守數據!AF50</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E49" s="1">
         <f>[1]攻守數據!AG50</f>
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="F49" s="1" t="str">
         <f>[1]攻守數據!AH50</f>
@@ -5066,7 +5341,7 @@
       </c>
       <c r="C50" s="1" t="str">
         <f>[1]攻守數據!AE51</f>
-        <v>龍</v>
+        <v>超能力</v>
       </c>
       <c r="D50" s="1" t="str">
         <f>[1]攻守數據!AF51</f>
@@ -5084,11 +5359,11 @@
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="str">
         <f>[1]攻守數據!AD52</f>
-        <v>高傲雉雞</v>
+        <v>拉帝亞斯</v>
       </c>
       <c r="C51" s="1" t="str">
         <f>[1]攻守數據!AE52</f>
-        <v>飛行</v>
+        <v>龍</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>[1]攻守數據!AF52</f>
@@ -5096,7 +5371,7 @@
       </c>
       <c r="E51" s="1">
         <f>[1]攻守數據!AG52</f>
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="F51" s="1" t="str">
         <f>[1]攻守數據!AH52</f>
@@ -5106,11 +5381,11 @@
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="str">
         <f>[1]攻守數據!AD53</f>
-        <v>超極巨巴大蝶</v>
+        <v>高傲雉雞</v>
       </c>
       <c r="C52" s="1" t="str">
         <f>[1]攻守數據!AE53</f>
-        <v>蟲</v>
+        <v>飛行</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>[1]攻守數據!AF53</f>
@@ -5118,17 +5393,17 @@
       </c>
       <c r="E52" s="1">
         <f>[1]攻守數據!AG53</f>
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="F52" s="1" t="str">
         <f>[1]攻守數據!AH53</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="str">
         <f>[1]攻守數據!AD54</f>
-        <v>巴大蝶</v>
+        <v>超極巨巴大蝶</v>
       </c>
       <c r="C53" s="1" t="str">
         <f>[1]攻守數據!AE54</f>
@@ -5144,7 +5419,7 @@
       </c>
       <c r="F53" s="1" t="str">
         <f>[1]攻守數據!AH54</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
@@ -5154,11 +5429,11 @@
       </c>
       <c r="C54" s="1" t="str">
         <f>[1]攻守數據!AE55</f>
-        <v>超能力</v>
+        <v>蟲</v>
       </c>
       <c r="D54" s="1" t="str">
         <f>[1]攻守數據!AF55</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E54" s="1">
         <f>[1]攻守數據!AG55</f>
@@ -5172,11 +5447,11 @@
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="str">
         <f>[1]攻守數據!AD56</f>
-        <v>藏飽栗鼠</v>
+        <v>巴大蝶</v>
       </c>
       <c r="C55" s="1" t="str">
         <f>[1]攻守數據!AE56</f>
-        <v>草</v>
+        <v>超能力</v>
       </c>
       <c r="D55" s="1" t="str">
         <f>[1]攻守數據!AF56</f>
@@ -5184,7 +5459,7 @@
       </c>
       <c r="E55" s="1">
         <f>[1]攻守數據!AG56</f>
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F55" s="1" t="str">
         <f>[1]攻守數據!AH56</f>
@@ -5194,11 +5469,11 @@
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="str">
         <f>[1]攻守數據!AD57</f>
-        <v>毛毛角羊</v>
+        <v>藏飽栗鼠</v>
       </c>
       <c r="C56" s="1" t="str">
         <f>[1]攻守數據!AE57</f>
-        <v>格鬥</v>
+        <v>草</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>[1]攻守數據!AF57</f>
@@ -5206,7 +5481,7 @@
       </c>
       <c r="E56" s="1">
         <f>[1]攻守數據!AG57</f>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F56" s="1" t="str">
         <f>[1]攻守數據!AH57</f>
@@ -5216,29 +5491,29 @@
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="str">
         <f>[1]攻守數據!AD58</f>
-        <v>超極巨千面避役</v>
+        <v>毛毛角羊</v>
       </c>
       <c r="C57" s="1" t="str">
         <f>[1]攻守數據!AE58</f>
-        <v>水</v>
+        <v>格鬥</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>[1]攻守數據!AF58</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E57" s="1">
         <f>[1]攻守數據!AG58</f>
-        <v>217</v>
+        <v>136</v>
       </c>
       <c r="F57" s="1" t="str">
         <f>[1]攻守數據!AH58</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="str">
         <f>[1]攻守數據!AD59</f>
-        <v>千面避役</v>
+        <v>超極巨千面避役</v>
       </c>
       <c r="C58" s="1" t="str">
         <f>[1]攻守數據!AE59</f>
@@ -5254,13 +5529,13 @@
       </c>
       <c r="F58" s="1" t="str">
         <f>[1]攻守數據!AH59</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="str">
         <f>[1]攻守數據!AD60</f>
-        <v>超極巨巨鉗蟹</v>
+        <v>千面避役</v>
       </c>
       <c r="C59" s="1" t="str">
         <f>[1]攻守數據!AE60</f>
@@ -5272,25 +5547,25 @@
       </c>
       <c r="E59" s="1">
         <f>[1]攻守數據!AG60</f>
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="F59" s="1" t="str">
         <f>[1]攻守數據!AH60</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="str">
         <f>[1]攻守數據!AD61</f>
-        <v>巨鉗蟹</v>
+        <v>超極巨巨鉗蟹</v>
       </c>
       <c r="C60" s="1" t="str">
         <f>[1]攻守數據!AE61</f>
-        <v>地面</v>
+        <v>水</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>[1]攻守數據!AF61</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E60" s="1">
         <f>[1]攻守數據!AG61</f>
@@ -5298,7 +5573,7 @@
       </c>
       <c r="F60" s="1" t="str">
         <f>[1]攻守數據!AH61</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
@@ -5308,7 +5583,7 @@
       </c>
       <c r="C61" s="1" t="str">
         <f>[1]攻守數據!AE62</f>
-        <v>鋼</v>
+        <v>地面</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>[1]攻守數據!AF62</f>
@@ -5326,7 +5601,7 @@
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="str">
         <f>[1]攻守數據!AD63</f>
-        <v>高傲雉雞</v>
+        <v>巨鉗蟹</v>
       </c>
       <c r="C62" s="1" t="str">
         <f>[1]攻守數據!AE63</f>
@@ -5338,7 +5613,7 @@
       </c>
       <c r="E62" s="1">
         <f>[1]攻守數據!AG63</f>
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F62" s="1" t="str">
         <f>[1]攻守數據!AH63</f>
@@ -5348,11 +5623,11 @@
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="str">
         <f>[1]攻守數據!AD64</f>
-        <v>鐮刀盔</v>
+        <v>高傲雉雞</v>
       </c>
       <c r="C63" s="1" t="str">
         <f>[1]攻守數據!AE64</f>
-        <v>地面</v>
+        <v>鋼</v>
       </c>
       <c r="D63" s="1" t="str">
         <f>[1]攻守數據!AF64</f>
@@ -5360,7 +5635,7 @@
       </c>
       <c r="E63" s="1">
         <f>[1]攻守數據!AG64</f>
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F63" s="1" t="str">
         <f>[1]攻守數據!AH64</f>
@@ -5374,7 +5649,7 @@
       </c>
       <c r="C64" s="1" t="str">
         <f>[1]攻守數據!AE65</f>
-        <v>蟲</v>
+        <v>地面</v>
       </c>
       <c r="D64" s="1" t="str">
         <f>[1]攻守數據!AF65</f>
@@ -5392,11 +5667,11 @@
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="str">
         <f>[1]攻守數據!AD66</f>
-        <v>多刺菊石獸</v>
+        <v>鐮刀盔</v>
       </c>
       <c r="C65" s="1" t="str">
         <f>[1]攻守數據!AE66</f>
-        <v>地面</v>
+        <v>蟲</v>
       </c>
       <c r="D65" s="1" t="str">
         <f>[1]攻守數據!AF66</f>
@@ -5404,7 +5679,7 @@
       </c>
       <c r="E65" s="1">
         <f>[1]攻守數據!AG66</f>
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F65" s="1" t="str">
         <f>[1]攻守數據!AH66</f>
@@ -5414,19 +5689,19 @@
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="str">
         <f>[1]攻守數據!AD67</f>
-        <v>巴大蝶</v>
+        <v>多刺菊石獸</v>
       </c>
       <c r="C66" s="1" t="str">
         <f>[1]攻守數據!AE67</f>
-        <v>蟲</v>
+        <v>地面</v>
       </c>
       <c r="D66" s="1" t="str">
         <f>[1]攻守數據!AF67</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E66" s="1">
         <f>[1]攻守數據!AG67</f>
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="F66" s="1" t="str">
         <f>[1]攻守數據!AH67</f>
@@ -5436,11 +5711,11 @@
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="str">
         <f>[1]攻守數據!AD68</f>
-        <v>鋼鎧鴉</v>
+        <v>巴大蝶</v>
       </c>
       <c r="C67" s="1" t="str">
         <f>[1]攻守數據!AE68</f>
-        <v>飛行</v>
+        <v>蟲</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>[1]攻守數據!AF68</f>
@@ -5448,7 +5723,7 @@
       </c>
       <c r="E67" s="1">
         <f>[1]攻守數據!AG68</f>
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F67" s="1" t="str">
         <f>[1]攻守數據!AH68</f>
@@ -5462,7 +5737,7 @@
       </c>
       <c r="C68" s="1" t="str">
         <f>[1]攻守數據!AE69</f>
-        <v>鋼</v>
+        <v>飛行</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>[1]攻守數據!AF69</f>
@@ -5484,11 +5759,11 @@
       </c>
       <c r="C69" s="1" t="str">
         <f>[1]攻守數據!AE70</f>
-        <v>地面</v>
+        <v>鋼</v>
       </c>
       <c r="D69" s="1" t="str">
         <f>[1]攻守數據!AF70</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E69" s="1">
         <f>[1]攻守數據!AG70</f>
@@ -5502,37 +5777,37 @@
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="str">
         <f>[1]攻守數據!AD71</f>
-        <v>超極巨灰塵山</v>
+        <v>鋼鎧鴉</v>
       </c>
       <c r="C70" s="1" t="str">
         <f>[1]攻守數據!AE71</f>
-        <v>毒</v>
+        <v>地面</v>
       </c>
       <c r="D70" s="1" t="str">
         <f>[1]攻守數據!AF71</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E70" s="1">
         <f>[1]攻守數據!AG71</f>
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="F70" s="1" t="str">
         <f>[1]攻守數據!AH71</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="str">
         <f>[1]攻守數據!AD72</f>
-        <v>灰塵山</v>
+        <v>超極巨灰塵山</v>
       </c>
       <c r="C71" s="1" t="str">
         <f>[1]攻守數據!AE72</f>
-        <v>蟲</v>
+        <v>毒</v>
       </c>
       <c r="D71" s="1" t="str">
         <f>[1]攻守數據!AF72</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E71" s="1">
         <f>[1]攻守數據!AG72</f>
@@ -5540,17 +5815,17 @@
       </c>
       <c r="F71" s="1" t="str">
         <f>[1]攻守數據!AH72</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="str">
         <f>[1]攻守數據!AD73</f>
-        <v>吼鯨王</v>
+        <v>灰塵山</v>
       </c>
       <c r="C72" s="1" t="str">
         <f>[1]攻守數據!AE73</f>
-        <v>超能力</v>
+        <v>蟲</v>
       </c>
       <c r="D72" s="1" t="str">
         <f>[1]攻守數據!AF73</f>
@@ -5558,7 +5833,7 @@
       </c>
       <c r="E72" s="1">
         <f>[1]攻守數據!AG73</f>
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F72" s="1" t="str">
         <f>[1]攻守數據!AH73</f>
@@ -5568,29 +5843,29 @@
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="str">
         <f>[1]攻守數據!AD74</f>
-        <v>超極巨水箭龜</v>
+        <v>吼鯨王</v>
       </c>
       <c r="C73" s="1" t="str">
         <f>[1]攻守數據!AE74</f>
-        <v>水</v>
+        <v>超能力</v>
       </c>
       <c r="D73" s="1" t="str">
         <f>[1]攻守數據!AF74</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E73" s="1">
         <f>[1]攻守數據!AG74</f>
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F73" s="1" t="str">
         <f>[1]攻守數據!AH74</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="str">
         <f>[1]攻守數據!AD75</f>
-        <v>水箭龜</v>
+        <v>超極巨水箭龜</v>
       </c>
       <c r="C74" s="1" t="str">
         <f>[1]攻守數據!AE75</f>
@@ -5606,7 +5881,7 @@
       </c>
       <c r="F74" s="1" t="str">
         <f>[1]攻守數據!AH75</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.3">
@@ -5616,11 +5891,11 @@
       </c>
       <c r="C75" s="1" t="str">
         <f>[1]攻守數據!AE76</f>
-        <v>岩石</v>
+        <v>水</v>
       </c>
       <c r="D75" s="1" t="str">
         <f>[1]攻守數據!AF76</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E75" s="1">
         <f>[1]攻守數據!AG76</f>
@@ -5638,7 +5913,7 @@
       </c>
       <c r="C76" s="1" t="str">
         <f>[1]攻守數據!AE77</f>
-        <v>惡</v>
+        <v>岩石</v>
       </c>
       <c r="D76" s="1" t="str">
         <f>[1]攻守數據!AF77</f>
@@ -5656,19 +5931,19 @@
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="str">
         <f>[1]攻守數據!AD78</f>
-        <v>勾魂眼</v>
+        <v>水箭龜</v>
       </c>
       <c r="C77" s="1" t="str">
         <f>[1]攻守數據!AE78</f>
-        <v>幽靈</v>
+        <v>惡</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>[1]攻守數據!AF78</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E77" s="1">
         <f>[1]攻守數據!AG78</f>
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="F77" s="1" t="str">
         <f>[1]攻守數據!AH78</f>
@@ -5682,7 +5957,7 @@
       </c>
       <c r="C78" s="1" t="str">
         <f>[1]攻守數據!AE79</f>
-        <v>惡</v>
+        <v>幽靈</v>
       </c>
       <c r="D78" s="1" t="str">
         <f>[1]攻守數據!AF79</f>
@@ -5700,11 +5975,11 @@
     <row r="79" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="str">
         <f>[1]攻守數據!AD80</f>
-        <v>鐮刀盔</v>
+        <v>勾魂眼</v>
       </c>
       <c r="C79" s="1" t="str">
         <f>[1]攻守數據!AE80</f>
-        <v>水</v>
+        <v>惡</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>[1]攻守數據!AF80</f>
@@ -5712,7 +5987,7 @@
       </c>
       <c r="E79" s="1">
         <f>[1]攻守數據!AG80</f>
-        <v>185</v>
+        <v>121</v>
       </c>
       <c r="F79" s="1" t="str">
         <f>[1]攻守數據!AH80</f>
@@ -5722,19 +5997,19 @@
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="str">
         <f>[1]攻守數據!AD81</f>
-        <v>藏飽栗鼠</v>
+        <v>鐮刀盔</v>
       </c>
       <c r="C80" s="1" t="str">
         <f>[1]攻守數據!AE81</f>
-        <v>地面</v>
+        <v>水</v>
       </c>
       <c r="D80" s="1" t="str">
         <f>[1]攻守數據!AF81</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E80" s="1">
         <f>[1]攻守數據!AG81</f>
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="F80" s="1" t="str">
         <f>[1]攻守數據!AH81</f>
@@ -5748,7 +6023,7 @@
       </c>
       <c r="C81" s="1" t="str">
         <f>[1]攻守數據!AE82</f>
-        <v>惡</v>
+        <v>地面</v>
       </c>
       <c r="D81" s="1" t="str">
         <f>[1]攻守數據!AF82</f>
@@ -5766,19 +6041,19 @@
     <row r="82" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="str">
         <f>[1]攻守數據!AD83</f>
-        <v>多刺菊石獸</v>
+        <v>藏飽栗鼠</v>
       </c>
       <c r="C82" s="1" t="str">
         <f>[1]攻守數據!AE83</f>
-        <v>水</v>
+        <v>惡</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>[1]攻守數據!AF83</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E82" s="1">
         <f>[1]攻守數據!AG83</f>
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="F82" s="1" t="str">
         <f>[1]攻守數據!AH83</f>
@@ -5788,7 +6063,7 @@
     <row r="83" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="str">
         <f>[1]攻守數據!AD84</f>
-        <v>水君</v>
+        <v>多刺菊石獸</v>
       </c>
       <c r="C83" s="1" t="str">
         <f>[1]攻守數據!AE84</f>
@@ -5800,7 +6075,7 @@
       </c>
       <c r="E83" s="1">
         <f>[1]攻守數據!AG84</f>
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="F83" s="1" t="str">
         <f>[1]攻守數據!AH84</f>
@@ -5810,7 +6085,7 @@
     <row r="84" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="str">
         <f>[1]攻守數據!AD85</f>
-        <v>吼鯨王</v>
+        <v>水君</v>
       </c>
       <c r="C84" s="1" t="str">
         <f>[1]攻守數據!AE85</f>
@@ -5832,19 +6107,19 @@
     <row r="85" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="str">
         <f>[1]攻守數據!AD86</f>
-        <v>幸福蛋</v>
+        <v>吼鯨王</v>
       </c>
       <c r="C85" s="1" t="str">
         <f>[1]攻守數據!AE86</f>
-        <v>超能力</v>
+        <v>水</v>
       </c>
       <c r="D85" s="1" t="str">
         <f>[1]攻守數據!AF86</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E85" s="1">
         <f>[1]攻守數據!AG86</f>
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="F85" s="1" t="str">
         <f>[1]攻守數據!AH86</f>
@@ -5854,19 +6129,19 @@
     <row r="86" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="str">
         <f>[1]攻守數據!AD87</f>
-        <v>急凍鳥</v>
+        <v>幸福蛋</v>
       </c>
       <c r="C86" s="1" t="str">
         <f>[1]攻守數據!AE87</f>
-        <v>冰</v>
+        <v>超能力</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>[1]攻守數據!AF87</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E86" s="1">
         <f>[1]攻守數據!AG87</f>
-        <v>155</v>
+        <v>113</v>
       </c>
       <c r="F86" s="1" t="str">
         <f>[1]攻守數據!AH87</f>
@@ -5876,7 +6151,7 @@
     <row r="87" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="str">
         <f>[1]攻守數據!AD88</f>
-        <v>幾何雪花</v>
+        <v>急凍鳥</v>
       </c>
       <c r="C87" s="1" t="str">
         <f>[1]攻守數據!AE88</f>
@@ -5888,7 +6163,7 @@
       </c>
       <c r="E87" s="1">
         <f>[1]攻守數據!AG88</f>
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F87" s="1" t="str">
         <f>[1]攻守數據!AH88</f>
@@ -5898,11 +6173,11 @@
     <row r="88" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="str">
         <f>[1]攻守數據!AD89</f>
-        <v>壺壺</v>
+        <v>幾何雪花</v>
       </c>
       <c r="C88" s="1" t="str">
         <f>[1]攻守數據!AE89</f>
-        <v>岩石</v>
+        <v>冰</v>
       </c>
       <c r="D88" s="1" t="str">
         <f>[1]攻守數據!AF89</f>
@@ -5910,7 +6185,7 @@
       </c>
       <c r="E88" s="1">
         <f>[1]攻守數據!AG89</f>
-        <v>17</v>
+        <v>153</v>
       </c>
       <c r="F88" s="1" t="str">
         <f>[1]攻守數據!AH89</f>
@@ -5924,7 +6199,7 @@
       </c>
       <c r="C89" s="1" t="str">
         <f>[1]攻守數據!AE90</f>
-        <v>蟲</v>
+        <v>岩石</v>
       </c>
       <c r="D89" s="1" t="str">
         <f>[1]攻守數據!AF90</f>
@@ -5942,11 +6217,11 @@
     <row r="90" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="str">
         <f>[1]攻守數據!AD91</f>
-        <v>胡地</v>
+        <v>壺壺</v>
       </c>
       <c r="C90" s="1" t="str">
         <f>[1]攻守數據!AE91</f>
-        <v>超能力</v>
+        <v>蟲</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>[1]攻守數據!AF91</f>
@@ -5954,7 +6229,7 @@
       </c>
       <c r="E90" s="1">
         <f>[1]攻守數據!AG91</f>
-        <v>225</v>
+        <v>17</v>
       </c>
       <c r="F90" s="1" t="str">
         <f>[1]攻守數據!AH91</f>
@@ -5968,11 +6243,11 @@
       </c>
       <c r="C91" s="1" t="str">
         <f>[1]攻守數據!AE92</f>
-        <v>格鬥</v>
+        <v>超能力</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>[1]攻守數據!AF92</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E91" s="1">
         <f>[1]攻守數據!AG92</f>
@@ -5986,19 +6261,19 @@
     <row r="92" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="str">
         <f>[1]攻守數據!AD93</f>
-        <v>拉普拉斯</v>
+        <v>胡地</v>
       </c>
       <c r="C92" s="1" t="str">
         <f>[1]攻守數據!AE93</f>
-        <v>冰</v>
+        <v>格鬥</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>[1]攻守數據!AF93</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E92" s="1">
         <f>[1]攻守數據!AG93</f>
-        <v>141</v>
+        <v>225</v>
       </c>
       <c r="F92" s="1" t="str">
         <f>[1]攻守數據!AH93</f>
@@ -6008,11 +6283,11 @@
     <row r="93" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="str">
         <f>[1]攻守數據!AD94</f>
-        <v>鋁鋼龍</v>
+        <v>超極巨拉普拉斯</v>
       </c>
       <c r="C93" s="1" t="str">
         <f>[1]攻守數據!AE94</f>
-        <v>鋼</v>
+        <v>冰</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>[1]攻守數據!AF94</f>
@@ -6020,11 +6295,11 @@
       </c>
       <c r="E93" s="1">
         <f>[1]攻守數據!AG94</f>
-        <v>201</v>
+        <v>141</v>
       </c>
       <c r="F93" s="1" t="str">
         <f>[1]攻守數據!AH94</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.3">
@@ -6034,7 +6309,7 @@
       </c>
       <c r="C94" s="1" t="str">
         <f>[1]攻守數據!AE95</f>
-        <v>龍</v>
+        <v>鋼</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>[1]攻守數據!AF95</f>
@@ -6056,11 +6331,11 @@
       </c>
       <c r="C95" s="1" t="str">
         <f>[1]攻守數據!AE96</f>
-        <v>一般</v>
+        <v>龍</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>[1]攻守數據!AF96</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E95" s="1">
         <f>[1]攻守數據!AG96</f>
@@ -6074,11 +6349,11 @@
     <row r="96" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="str">
         <f>[1]攻守數據!AD97</f>
-        <v>巨金怪</v>
+        <v>鋁鋼龍</v>
       </c>
       <c r="C96" s="1" t="str">
         <f>[1]攻守數據!AE97</f>
-        <v>幽靈</v>
+        <v>一般</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>[1]攻守數據!AF97</f>
@@ -6086,7 +6361,7 @@
       </c>
       <c r="E96" s="1">
         <f>[1]攻守數據!AG97</f>
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="F96" s="1" t="str">
         <f>[1]攻守數據!AH97</f>
@@ -6096,19 +6371,19 @@
     <row r="97" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="str">
         <f>[1]攻守數據!AD98</f>
-        <v>沙奈朵</v>
+        <v>巨金怪</v>
       </c>
       <c r="C97" s="1" t="str">
         <f>[1]攻守數據!AE98</f>
-        <v>妖精</v>
+        <v>幽靈</v>
       </c>
       <c r="D97" s="1" t="str">
         <f>[1]攻守數據!AF98</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E97" s="1">
         <f>[1]攻守數據!AG98</f>
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="F97" s="1" t="str">
         <f>[1]攻守數據!AH98</f>
@@ -6122,7 +6397,7 @@
       </c>
       <c r="C98" s="1" t="str">
         <f>[1]攻守數據!AE99</f>
-        <v>超能力</v>
+        <v>妖精</v>
       </c>
       <c r="D98" s="1" t="str">
         <f>[1]攻守數據!AF99</f>
@@ -6144,11 +6419,11 @@
       </c>
       <c r="C99" s="1" t="str">
         <f>[1]攻守數據!AE100</f>
-        <v>草</v>
+        <v>超能力</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>[1]攻守數據!AF100</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E99" s="1">
         <f>[1]攻守數據!AG100</f>
@@ -6166,7 +6441,7 @@
       </c>
       <c r="C100" s="1" t="str">
         <f>[1]攻守數據!AE101</f>
-        <v>電</v>
+        <v>草</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>[1]攻守數據!AF101</f>
@@ -6184,19 +6459,19 @@
     <row r="101" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="str">
         <f>[1]攻守數據!AD102</f>
-        <v>甜冷美后</v>
+        <v>沙奈朵</v>
       </c>
       <c r="C101" s="1" t="str">
         <f>[1]攻守數據!AE102</f>
-        <v>草</v>
+        <v>電</v>
       </c>
       <c r="D101" s="1" t="str">
         <f>[1]攻守數據!AF102</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E101" s="1">
         <f>[1]攻守數據!AG102</f>
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="F101" s="1" t="str">
         <f>[1]攻守數據!AH102</f>
@@ -6210,11 +6485,11 @@
       </c>
       <c r="C102" s="1" t="str">
         <f>[1]攻守數據!AE103</f>
-        <v>妖精</v>
+        <v>草</v>
       </c>
       <c r="D102" s="1" t="str">
         <f>[1]攻守數據!AF103</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E102" s="1">
         <f>[1]攻守數據!AG103</f>
@@ -6228,33 +6503,33 @@
     <row r="103" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="str">
         <f>[1]攻守數據!AD104</f>
-        <v>超極巨伊布</v>
+        <v>甜冷美后</v>
       </c>
       <c r="C103" s="1" t="str">
         <f>[1]攻守數據!AE104</f>
-        <v>一般</v>
+        <v>妖精</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>[1]攻守數據!AF104</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E103" s="1">
         <f>[1]攻守數據!AG104</f>
-        <v>94</v>
+        <v>187</v>
       </c>
       <c r="F103" s="1" t="str">
         <f>[1]攻守數據!AH104</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="str">
         <f>[1]攻守數據!AD105</f>
-        <v>水伊布</v>
+        <v>超極巨伊布</v>
       </c>
       <c r="C104" s="1" t="str">
         <f>[1]攻守數據!AE105</f>
-        <v>水</v>
+        <v>一般</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>[1]攻守數據!AF105</f>
@@ -6262,21 +6537,21 @@
       </c>
       <c r="E104" s="1">
         <f>[1]攻守數據!AG105</f>
-        <v>174</v>
+        <v>94</v>
       </c>
       <c r="F104" s="1" t="str">
         <f>[1]攻守數據!AH105</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B105" s="1" t="str">
         <f>[1]攻守數據!AD106</f>
-        <v>雷伊布</v>
+        <v>水伊布</v>
       </c>
       <c r="C105" s="1" t="str">
         <f>[1]攻守數據!AE106</f>
-        <v>電</v>
+        <v>水</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>[1]攻守數據!AF106</f>
@@ -6284,7 +6559,7 @@
       </c>
       <c r="E105" s="1">
         <f>[1]攻守數據!AG106</f>
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="F105" s="1" t="str">
         <f>[1]攻守數據!AH106</f>
@@ -6294,11 +6569,11 @@
     <row r="106" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B106" s="1" t="str">
         <f>[1]攻守數據!AD107</f>
-        <v>火伊布</v>
+        <v>雷伊布</v>
       </c>
       <c r="C106" s="1" t="str">
         <f>[1]攻守數據!AE107</f>
-        <v>火</v>
+        <v>電</v>
       </c>
       <c r="D106" s="1" t="str">
         <f>[1]攻守數據!AF107</f>
@@ -6306,7 +6581,7 @@
       </c>
       <c r="E106" s="1">
         <f>[1]攻守數據!AG107</f>
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="F106" s="1" t="str">
         <f>[1]攻守數據!AH107</f>
@@ -6316,11 +6591,11 @@
     <row r="107" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B107" s="1" t="str">
         <f>[1]攻守數據!AD108</f>
-        <v>太陽伊布</v>
+        <v>火伊布</v>
       </c>
       <c r="C107" s="1" t="str">
         <f>[1]攻守數據!AE108</f>
-        <v>超能力</v>
+        <v>火</v>
       </c>
       <c r="D107" s="1" t="str">
         <f>[1]攻守數據!AF108</f>
@@ -6328,7 +6603,7 @@
       </c>
       <c r="E107" s="1">
         <f>[1]攻守數據!AG108</f>
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="F107" s="1" t="str">
         <f>[1]攻守數據!AH108</f>
@@ -6338,11 +6613,11 @@
     <row r="108" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B108" s="1" t="str">
         <f>[1]攻守數據!AD109</f>
-        <v>月亮伊布</v>
+        <v>太陽伊布</v>
       </c>
       <c r="C108" s="1" t="str">
         <f>[1]攻守數據!AE109</f>
-        <v>惡</v>
+        <v>超能力</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>[1]攻守數據!AF109</f>
@@ -6350,7 +6625,7 @@
       </c>
       <c r="E108" s="1">
         <f>[1]攻守數據!AG109</f>
-        <v>111</v>
+        <v>218</v>
       </c>
       <c r="F108" s="1" t="str">
         <f>[1]攻守數據!AH109</f>
@@ -6360,11 +6635,11 @@
     <row r="109" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B109" s="1" t="str">
         <f>[1]攻守數據!AD110</f>
-        <v>葉伊布</v>
+        <v>月亮伊布</v>
       </c>
       <c r="C109" s="1" t="str">
         <f>[1]攻守數據!AE110</f>
-        <v>草</v>
+        <v>惡</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>[1]攻守數據!AF110</f>
@@ -6372,7 +6647,7 @@
       </c>
       <c r="E109" s="1">
         <f>[1]攻守數據!AG110</f>
-        <v>183</v>
+        <v>111</v>
       </c>
       <c r="F109" s="1" t="str">
         <f>[1]攻守數據!AH110</f>
@@ -6382,11 +6657,11 @@
     <row r="110" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B110" s="1" t="str">
         <f>[1]攻守數據!AD111</f>
-        <v>冰伊布</v>
+        <v>葉伊布</v>
       </c>
       <c r="C110" s="1" t="str">
         <f>[1]攻守數據!AE111</f>
-        <v>冰</v>
+        <v>草</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>[1]攻守數據!AF111</f>
@@ -6394,7 +6669,7 @@
       </c>
       <c r="E110" s="1">
         <f>[1]攻守數據!AG111</f>
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="F110" s="1" t="str">
         <f>[1]攻守數據!AH111</f>
@@ -6404,11 +6679,11 @@
     <row r="111" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B111" s="1" t="str">
         <f>[1]攻守數據!AD112</f>
-        <v>仙子伊布</v>
+        <v>冰伊布</v>
       </c>
       <c r="C111" s="1" t="str">
         <f>[1]攻守數據!AE112</f>
-        <v>妖精</v>
+        <v>冰</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>[1]攻守數據!AF112</f>
@@ -6416,7 +6691,7 @@
       </c>
       <c r="E111" s="1">
         <f>[1]攻守數據!AG112</f>
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="F111" s="1" t="str">
         <f>[1]攻守數據!AH112</f>
@@ -6426,11 +6701,11 @@
     <row r="112" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B112" s="1" t="str">
         <f>[1]攻守數據!AD113</f>
-        <v>艾路雷朵</v>
+        <v>仙子伊布</v>
       </c>
       <c r="C112" s="1" t="str">
         <f>[1]攻守數據!AE113</f>
-        <v>格鬥</v>
+        <v>妖精</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>[1]攻守數據!AF113</f>
@@ -6438,7 +6713,7 @@
       </c>
       <c r="E112" s="1">
         <f>[1]攻守數據!AG113</f>
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="F112" s="1" t="str">
         <f>[1]攻守數據!AH113</f>
@@ -6452,7 +6727,7 @@
       </c>
       <c r="C113" s="1" t="str">
         <f>[1]攻守數據!AE114</f>
-        <v>超能力</v>
+        <v>格鬥</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>[1]攻守數據!AF114</f>
@@ -6474,11 +6749,11 @@
       </c>
       <c r="C114" s="1" t="str">
         <f>[1]攻守數據!AE115</f>
-        <v>妖精</v>
+        <v>超能力</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>[1]攻守數據!AF115</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E114" s="1">
         <f>[1]攻守數據!AG115</f>
@@ -6492,19 +6767,19 @@
     <row r="115" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B115" s="1" t="str">
         <f>[1]攻守數據!AD116</f>
-        <v>烏賊王</v>
+        <v>艾路雷朵</v>
       </c>
       <c r="C115" s="1" t="str">
         <f>[1]攻守數據!AE116</f>
-        <v>超能力</v>
+        <v>妖精</v>
       </c>
       <c r="D115" s="1" t="str">
         <f>[1]攻守數據!AF116</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E115" s="1">
         <f>[1]攻守數據!AG116</f>
-        <v>151</v>
+        <v>199</v>
       </c>
       <c r="F115" s="1" t="str">
         <f>[1]攻守數據!AH116</f>
@@ -6518,11 +6793,11 @@
       </c>
       <c r="C116" s="1" t="str">
         <f>[1]攻守數據!AE117</f>
-        <v>飛行</v>
+        <v>超能力</v>
       </c>
       <c r="D116" s="1" t="str">
         <f>[1]攻守數據!AF117</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E116" s="1">
         <f>[1]攻守數據!AG117</f>
@@ -6536,19 +6811,19 @@
     <row r="117" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B117" s="1" t="str">
         <f>[1]攻守數據!AD118</f>
-        <v>洛奇亞</v>
+        <v>烏賊王</v>
       </c>
       <c r="C117" s="1" t="str">
         <f>[1]攻守數據!AE118</f>
-        <v>超能力</v>
+        <v>飛行</v>
       </c>
       <c r="D117" s="1" t="str">
         <f>[1]攻守數據!AF118</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E117" s="1">
         <f>[1]攻守數據!AG118</f>
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="F117" s="1" t="str">
         <f>[1]攻守數據!AH118</f>
@@ -6562,11 +6837,11 @@
       </c>
       <c r="C118" s="1" t="str">
         <f>[1]攻守數據!AE119</f>
-        <v>龍</v>
+        <v>超能力</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>[1]攻守數據!AF119</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E118" s="1">
         <f>[1]攻守數據!AG119</f>
@@ -6580,19 +6855,19 @@
     <row r="119" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B119" s="1" t="str">
         <f>[1]攻守數據!AD120</f>
-        <v>飛腿郎</v>
+        <v>洛奇亞</v>
       </c>
       <c r="C119" s="1" t="str">
         <f>[1]攻守數據!AE120</f>
-        <v>格鬥</v>
+        <v>龍</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>[1]攻守數據!AF120</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E119" s="1">
         <f>[1]攻守數據!AG120</f>
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="F119" s="1" t="str">
         <f>[1]攻守數據!AH120</f>
@@ -6602,7 +6877,7 @@
     <row r="120" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B120" s="1" t="str">
         <f>[1]攻守數據!AD121</f>
-        <v>快拳郎</v>
+        <v>飛腿郎</v>
       </c>
       <c r="C120" s="1" t="str">
         <f>[1]攻守數據!AE121</f>
@@ -6614,7 +6889,7 @@
       </c>
       <c r="E120" s="1">
         <f>[1]攻守數據!AG121</f>
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="F120" s="1" t="str">
         <f>[1]攻守數據!AH121</f>
@@ -6628,11 +6903,11 @@
       </c>
       <c r="C121" s="1" t="str">
         <f>[1]攻守數據!AE122</f>
-        <v>鋼</v>
+        <v>格鬥</v>
       </c>
       <c r="D121" s="1" t="str">
         <f>[1]攻守數據!AF122</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E121" s="1">
         <f>[1]攻守數據!AG122</f>
@@ -6646,19 +6921,19 @@
     <row r="122" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B122" s="1" t="str">
         <f>[1]攻守數據!AD123</f>
-        <v>帝牙海獅</v>
+        <v>快拳郎</v>
       </c>
       <c r="C122" s="1" t="str">
         <f>[1]攻守數據!AE123</f>
-        <v>水</v>
+        <v>鋼</v>
       </c>
       <c r="D122" s="1" t="str">
         <f>[1]攻守數據!AF123</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E122" s="1">
         <f>[1]攻守數據!AG123</f>
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="F122" s="1" t="str">
         <f>[1]攻守數據!AH123</f>
@@ -6672,7 +6947,7 @@
       </c>
       <c r="C123" s="1" t="str">
         <f>[1]攻守數據!AE124</f>
-        <v>冰</v>
+        <v>水</v>
       </c>
       <c r="D123" s="1" t="str">
         <f>[1]攻守數據!AF124</f>
@@ -6690,11 +6965,11 @@
     <row r="124" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B124" s="1" t="str">
         <f>[1]攻守數據!AD125</f>
-        <v>龐岩怪</v>
+        <v>帝牙海獅</v>
       </c>
       <c r="C124" s="1" t="str">
         <f>[1]攻守數據!AE125</f>
-        <v>岩石</v>
+        <v>冰</v>
       </c>
       <c r="D124" s="1" t="str">
         <f>[1]攻守數據!AF125</f>
@@ -6702,7 +6977,7 @@
       </c>
       <c r="E124" s="1">
         <f>[1]攻守數據!AG125</f>
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="F124" s="1" t="str">
         <f>[1]攻守數據!AH125</f>
@@ -6712,11 +6987,11 @@
     <row r="125" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B125" s="14" t="str">
         <f>IF([1]攻守數據!AD129 = "", "", [1]攻守數據!AD129)</f>
-        <v>鳳王</v>
+        <v>老翁龍</v>
       </c>
       <c r="C125" s="14" t="str">
         <f>IF([1]攻守數據!AE129 = "", "", [1]攻守數據!AE129)</f>
-        <v>火</v>
+        <v>一般</v>
       </c>
       <c r="D125" s="14" t="str">
         <f>IF([1]攻守數據!AF129 = "", "", [1]攻守數據!AF129)</f>
@@ -6724,7 +6999,7 @@
       </c>
       <c r="E125" s="14">
         <f>IF([1]攻守數據!AG129 = "", "", [1]攻守數據!AG129)</f>
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F125" s="14" t="str">
         <f>IF([1]攻守數據!AH129 = "", "", [1]攻守數據!AH129)</f>
@@ -6738,11 +7013,11 @@
       </c>
       <c r="C126" s="14" t="str">
         <f>IF([1]攻守數據!AE130 = "", "", [1]攻守數據!AE130)</f>
-        <v>超能力</v>
+        <v>火</v>
       </c>
       <c r="D126" s="14" t="str">
         <f>IF([1]攻守數據!AF130 = "", "", [1]攻守數據!AF130)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E126" s="14">
         <f>IF([1]攻守數據!AG130 = "", "", [1]攻守數據!AG130)</f>
@@ -6760,7 +7035,7 @@
       </c>
       <c r="C127" s="14" t="str">
         <f>IF([1]攻守數據!AE131 = "", "", [1]攻守數據!AE131)</f>
-        <v>一般</v>
+        <v>超能力</v>
       </c>
       <c r="D127" s="14" t="str">
         <f>IF([1]攻守數據!AF131 = "", "", [1]攻守數據!AF131)</f>
@@ -6782,7 +7057,7 @@
       </c>
       <c r="C128" s="14" t="str">
         <f>IF([1]攻守數據!AE132 = "", "", [1]攻守數據!AE132)</f>
-        <v>鋼</v>
+        <v>一般</v>
       </c>
       <c r="D128" s="14" t="str">
         <f>IF([1]攻守數據!AF132 = "", "", [1]攻守數據!AF132)</f>
@@ -6800,353 +7075,353 @@
     <row r="129" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B129" s="14" t="str">
         <f>IF([1]攻守數據!AD133 = "", "", [1]攻守數據!AD133)</f>
-        <v/>
+        <v>鳳王</v>
       </c>
       <c r="C129" s="14" t="str">
         <f>IF([1]攻守數據!AE133 = "", "", [1]攻守數據!AE133)</f>
-        <v/>
+        <v>鋼</v>
       </c>
       <c r="D129" s="14" t="str">
         <f>IF([1]攻守數據!AF133 = "", "", [1]攻守數據!AF133)</f>
-        <v/>
-      </c>
-      <c r="E129" s="14" t="str">
+        <v>N</v>
+      </c>
+      <c r="E129" s="14">
         <f>IF([1]攻守數據!AG133 = "", "", [1]攻守數據!AG133)</f>
-        <v/>
+        <v>201</v>
       </c>
       <c r="F129" s="14" t="str">
         <f>IF([1]攻守數據!AH133 = "", "", [1]攻守數據!AH133)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="130" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B130" s="14" t="str">
         <f>IF([1]攻守數據!AD134 = "", "", [1]攻守數據!AD134)</f>
-        <v/>
+        <v>風速狗</v>
       </c>
       <c r="C130" s="14" t="str">
         <f>IF([1]攻守數據!AE134 = "", "", [1]攻守數據!AE134)</f>
-        <v/>
+        <v>火</v>
       </c>
       <c r="D130" s="14" t="str">
         <f>IF([1]攻守數據!AF134 = "", "", [1]攻守數據!AF134)</f>
-        <v/>
-      </c>
-      <c r="E130" s="14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E130" s="14">
         <f>IF([1]攻守數據!AG134 = "", "", [1]攻守數據!AG134)</f>
-        <v/>
+        <v>191</v>
       </c>
       <c r="F130" s="14" t="str">
         <f>IF([1]攻守數據!AH134 = "", "", [1]攻守數據!AH134)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="131" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B131" s="14" t="str">
         <f>IF([1]攻守數據!AD135 = "", "", [1]攻守數據!AD135)</f>
-        <v/>
+        <v>風速狗</v>
       </c>
       <c r="C131" s="14" t="str">
         <f>IF([1]攻守數據!AE135 = "", "", [1]攻守數據!AE135)</f>
-        <v/>
+        <v>惡</v>
       </c>
       <c r="D131" s="14" t="str">
         <f>IF([1]攻守數據!AF135 = "", "", [1]攻守數據!AF135)</f>
-        <v/>
-      </c>
-      <c r="E131" s="14" t="str">
+        <v>N</v>
+      </c>
+      <c r="E131" s="14">
         <f>IF([1]攻守數據!AG135 = "", "", [1]攻守數據!AG135)</f>
-        <v/>
+        <v>191</v>
       </c>
       <c r="F131" s="14" t="str">
         <f>IF([1]攻守數據!AH135 = "", "", [1]攻守數據!AH135)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="132" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B132" s="14" t="str">
         <f>IF([1]攻守數據!AD136 = "", "", [1]攻守數據!AD136)</f>
-        <v/>
+        <v>風速狗</v>
       </c>
       <c r="C132" s="14" t="str">
         <f>IF([1]攻守數據!AE136 = "", "", [1]攻守數據!AE136)</f>
-        <v/>
+        <v>電</v>
       </c>
       <c r="D132" s="14" t="str">
         <f>IF([1]攻守數據!AF136 = "", "", [1]攻守數據!AF136)</f>
-        <v/>
-      </c>
-      <c r="E132" s="14" t="str">
+        <v>N</v>
+      </c>
+      <c r="E132" s="14">
         <f>IF([1]攻守數據!AG136 = "", "", [1]攻守數據!AG136)</f>
-        <v/>
+        <v>191</v>
       </c>
       <c r="F132" s="14" t="str">
         <f>IF([1]攻守數據!AH136 = "", "", [1]攻守數據!AH136)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="133" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B133" s="14" t="str">
         <f>IF([1]攻守數據!AD137 = "", "", [1]攻守數據!AD137)</f>
-        <v/>
+        <v>固拉多</v>
       </c>
       <c r="C133" s="14" t="str">
         <f>IF([1]攻守數據!AE137 = "", "", [1]攻守數據!AE137)</f>
-        <v/>
+        <v>地面</v>
       </c>
       <c r="D133" s="14" t="str">
         <f>IF([1]攻守數據!AF137 = "", "", [1]攻守數據!AF137)</f>
-        <v/>
-      </c>
-      <c r="E133" s="14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E133" s="14">
         <f>IF([1]攻守數據!AG137 = "", "", [1]攻守數據!AG137)</f>
-        <v/>
+        <v>225</v>
       </c>
       <c r="F133" s="14" t="str">
         <f>IF([1]攻守數據!AH137 = "", "", [1]攻守數據!AH137)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="134" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B134" s="14" t="str">
         <f>IF([1]攻守數據!AD138 = "", "", [1]攻守數據!AD138)</f>
-        <v/>
+        <v>固拉多</v>
       </c>
       <c r="C134" s="14" t="str">
         <f>IF([1]攻守數據!AE138 = "", "", [1]攻守數據!AE138)</f>
-        <v/>
+        <v>龍</v>
       </c>
       <c r="D134" s="14" t="str">
         <f>IF([1]攻守數據!AF138 = "", "", [1]攻守數據!AF138)</f>
-        <v/>
-      </c>
-      <c r="E134" s="14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E134" s="14">
         <f>IF([1]攻守數據!AG138 = "", "", [1]攻守數據!AG138)</f>
-        <v/>
+        <v>225</v>
       </c>
       <c r="F134" s="14" t="str">
         <f>IF([1]攻守數據!AH138 = "", "", [1]攻守數據!AH138)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="135" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B135" s="14" t="str">
         <f>IF([1]攻守數據!AD139 = "", "", [1]攻守數據!AD139)</f>
-        <v/>
+        <v>蓋歐卡</v>
       </c>
       <c r="C135" s="14" t="str">
         <f>IF([1]攻守數據!AE139 = "", "", [1]攻守數據!AE139)</f>
-        <v/>
+        <v>水</v>
       </c>
       <c r="D135" s="14" t="str">
         <f>IF([1]攻守數據!AF139 = "", "", [1]攻守數據!AF139)</f>
-        <v/>
-      </c>
-      <c r="E135" s="14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E135" s="14">
         <f>IF([1]攻守數據!AG139 = "", "", [1]攻守數據!AG139)</f>
-        <v/>
+        <v>225</v>
       </c>
       <c r="F135" s="14" t="str">
         <f>IF([1]攻守數據!AH139 = "", "", [1]攻守數據!AH139)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="136" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B136" s="14" t="str">
         <f>IF([1]攻守數據!AD140 = "", "", [1]攻守數據!AD140)</f>
-        <v/>
+        <v>烈空坐</v>
       </c>
       <c r="C136" s="14" t="str">
         <f>IF([1]攻守數據!AE140 = "", "", [1]攻守數據!AE140)</f>
-        <v/>
+        <v>龍</v>
       </c>
       <c r="D136" s="14" t="str">
         <f>IF([1]攻守數據!AF140 = "", "", [1]攻守數據!AF140)</f>
-        <v/>
-      </c>
-      <c r="E136" s="14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E136" s="14">
         <f>IF([1]攻守數據!AG140 = "", "", [1]攻守數據!AG140)</f>
-        <v/>
+        <v>236</v>
       </c>
       <c r="F136" s="14" t="str">
         <f>IF([1]攻守數據!AH140 = "", "", [1]攻守數據!AH140)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="137" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B137" s="14" t="str">
         <f>IF([1]攻守數據!AD141 = "", "", [1]攻守數據!AD141)</f>
-        <v/>
+        <v>烈空坐</v>
       </c>
       <c r="C137" s="14" t="str">
         <f>IF([1]攻守數據!AE141 = "", "", [1]攻守數據!AE141)</f>
-        <v/>
+        <v>飛行</v>
       </c>
       <c r="D137" s="14" t="str">
         <f>IF([1]攻守數據!AF141 = "", "", [1]攻守數據!AF141)</f>
-        <v/>
-      </c>
-      <c r="E137" s="14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E137" s="14">
         <f>IF([1]攻守數據!AG141 = "", "", [1]攻守數據!AG141)</f>
-        <v/>
+        <v>236</v>
       </c>
       <c r="F137" s="14" t="str">
         <f>IF([1]攻守數據!AH141 = "", "", [1]攻守數據!AH141)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="138" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B138" s="14" t="str">
         <f>IF([1]攻守數據!AD142 = "", "", [1]攻守數據!AD142)</f>
-        <v/>
+        <v>喵喵</v>
       </c>
       <c r="C138" s="14" t="str">
         <f>IF([1]攻守數據!AE142 = "", "", [1]攻守數據!AE142)</f>
-        <v/>
+        <v>一般</v>
       </c>
       <c r="D138" s="14" t="str">
         <f>IF([1]攻守數據!AF142 = "", "", [1]攻守數據!AF142)</f>
-        <v/>
-      </c>
-      <c r="E138" s="14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E138" s="14">
         <f>IF([1]攻守數據!AG142 = "", "", [1]攻守數據!AG142)</f>
-        <v/>
+        <v>85</v>
       </c>
       <c r="F138" s="14" t="str">
         <f>IF([1]攻守數據!AH142 = "", "", [1]攻守數據!AH142)</f>
-        <v/>
+        <v>G</v>
       </c>
     </row>
     <row r="139" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B139" s="14" t="str">
         <f>IF([1]攻守數據!AD143 = "", "", [1]攻守數據!AD143)</f>
-        <v/>
+        <v>皮卡丘</v>
       </c>
       <c r="C139" s="14" t="str">
         <f>IF([1]攻守數據!AE143 = "", "", [1]攻守數據!AE143)</f>
-        <v/>
+        <v>電</v>
       </c>
       <c r="D139" s="14" t="str">
         <f>IF([1]攻守數據!AF143 = "", "", [1]攻守數據!AF143)</f>
-        <v/>
-      </c>
-      <c r="E139" s="14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E139" s="14">
         <f>IF([1]攻守數據!AG143 = "", "", [1]攻守數據!AG143)</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="F139" s="14" t="str">
         <f>IF([1]攻守數據!AH143 = "", "", [1]攻守數據!AH143)</f>
-        <v/>
+        <v>G</v>
       </c>
     </row>
     <row r="140" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B140" s="14" t="str">
         <f>IF([1]攻守數據!AD144 = "", "", [1]攻守數據!AD144)</f>
-        <v/>
+        <v>雷丘</v>
       </c>
       <c r="C140" s="14" t="str">
         <f>IF([1]攻守數據!AE144 = "", "", [1]攻守數據!AE144)</f>
-        <v/>
+        <v>電</v>
       </c>
       <c r="D140" s="14" t="str">
         <f>IF([1]攻守數據!AF144 = "", "", [1]攻守數據!AF144)</f>
-        <v/>
-      </c>
-      <c r="E140" s="14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E140" s="14">
         <f>IF([1]攻守數據!AG144 = "", "", [1]攻守數據!AG144)</f>
-        <v/>
+        <v>164</v>
       </c>
       <c r="F140" s="14" t="str">
         <f>IF([1]攻守數據!AH144 = "", "", [1]攻守數據!AH144)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="141" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B141" s="14" t="str">
         <f>IF([1]攻守數據!AD145 = "", "", [1]攻守數據!AD145)</f>
-        <v/>
+        <v>雷丘</v>
       </c>
       <c r="C141" s="14" t="str">
         <f>IF([1]攻守數據!AE145 = "", "", [1]攻守數據!AE145)</f>
-        <v/>
+        <v>妖精</v>
       </c>
       <c r="D141" s="14" t="str">
         <f>IF([1]攻守數據!AF145 = "", "", [1]攻守數據!AF145)</f>
-        <v/>
-      </c>
-      <c r="E141" s="14" t="str">
+        <v>N</v>
+      </c>
+      <c r="E141" s="14">
         <f>IF([1]攻守數據!AG145 = "", "", [1]攻守數據!AG145)</f>
-        <v/>
+        <v>164</v>
       </c>
       <c r="F141" s="14" t="str">
         <f>IF([1]攻守數據!AH145 = "", "", [1]攻守數據!AH145)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="142" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B142" s="14" t="str">
         <f>IF([1]攻守數據!AD146 = "", "", [1]攻守數據!AD146)</f>
-        <v/>
+        <v>雷吉艾斯</v>
       </c>
       <c r="C142" s="14" t="str">
         <f>IF([1]攻守數據!AE146 = "", "", [1]攻守數據!AE146)</f>
-        <v/>
+        <v>冰</v>
       </c>
       <c r="D142" s="14" t="str">
         <f>IF([1]攻守數據!AF146 = "", "", [1]攻守數據!AF146)</f>
-        <v/>
-      </c>
-      <c r="E142" s="14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E142" s="14">
         <f>IF([1]攻守數據!AG146 = "", "", [1]攻守數據!AG146)</f>
-        <v/>
+        <v>153</v>
       </c>
       <c r="F142" s="14" t="str">
         <f>IF([1]攻守數據!AH146 = "", "", [1]攻守數據!AH146)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="143" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B143" s="14" t="str">
         <f>IF([1]攻守數據!AD147 = "", "", [1]攻守數據!AD147)</f>
-        <v/>
+        <v>雷吉艾斯</v>
       </c>
       <c r="C143" s="14" t="str">
         <f>IF([1]攻守數據!AE147 = "", "", [1]攻守數據!AE147)</f>
-        <v/>
+        <v>一般</v>
       </c>
       <c r="D143" s="14" t="str">
         <f>IF([1]攻守數據!AF147 = "", "", [1]攻守數據!AF147)</f>
-        <v/>
-      </c>
-      <c r="E143" s="14" t="str">
+        <v>N</v>
+      </c>
+      <c r="E143" s="14">
         <f>IF([1]攻守數據!AG147 = "", "", [1]攻守數據!AG147)</f>
-        <v/>
+        <v>153</v>
       </c>
       <c r="F143" s="14" t="str">
         <f>IF([1]攻守數據!AH147 = "", "", [1]攻守數據!AH147)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="144" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B144" s="14" t="str">
         <f>IF([1]攻守數據!AD148 = "", "", [1]攻守數據!AD148)</f>
-        <v/>
+        <v>雷吉艾斯</v>
       </c>
       <c r="C144" s="14" t="str">
         <f>IF([1]攻守數據!AE148 = "", "", [1]攻守數據!AE148)</f>
-        <v/>
+        <v>格鬥</v>
       </c>
       <c r="D144" s="14" t="str">
         <f>IF([1]攻守數據!AF148 = "", "", [1]攻守數據!AF148)</f>
-        <v/>
-      </c>
-      <c r="E144" s="14" t="str">
+        <v>N</v>
+      </c>
+      <c r="E144" s="14">
         <f>IF([1]攻守數據!AG148 = "", "", [1]攻守數據!AG148)</f>
-        <v/>
+        <v>153</v>
       </c>
       <c r="F144" s="14" t="str">
         <f>IF([1]攻守數據!AH148 = "", "", [1]攻守數據!AH148)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.3">

--- a/Att.xlsx
+++ b/Att.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\寶可夢\Pokemon_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E082C6-69D7-4843-B473-57A67E0F51B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F184D24D-8AA4-4FE0-AB1E-02775F35AE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2873,16 +2873,19 @@
         </row>
         <row r="152">
           <cell r="AM152" t="str">
-            <v/>
+            <v>超極巨長毛巨魔</v>
           </cell>
           <cell r="AN152" t="str">
-            <v/>
-          </cell>
-          <cell r="AP152" t="str">
-            <v/>
+            <v>惡</v>
+          </cell>
+          <cell r="AO152" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP152">
+            <v>191</v>
           </cell>
           <cell r="AQ152" t="str">
-            <v/>
+            <v>G</v>
           </cell>
         </row>
         <row r="153">
@@ -7866,23 +7869,23 @@
     <row r="151" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B151" s="13" t="str">
         <f>IF([1]攻守數據!AM152 = "", "", [1]攻守數據!AM152)</f>
-        <v/>
+        <v>超極巨長毛巨魔</v>
       </c>
       <c r="C151" s="13" t="str">
         <f>IF([1]攻守數據!AN152 = "", "", [1]攻守數據!AN152)</f>
-        <v/>
+        <v>惡</v>
       </c>
       <c r="D151" s="13" t="str">
         <f>IF([1]攻守數據!AO152 = "", "", [1]攻守數據!AO152)</f>
-        <v/>
-      </c>
-      <c r="E151" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E151" s="13">
         <f>IF([1]攻守數據!AP152 = "", "", [1]攻守數據!AP152)</f>
-        <v/>
+        <v>191</v>
       </c>
       <c r="F151" s="13" t="str">
         <f>IF([1]攻守數據!AQ152 = "", "", [1]攻守數據!AQ152)</f>
-        <v/>
+        <v>G</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.3">

--- a/Att.xlsx
+++ b/Att.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\寶可夢\Pokemon_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F184D24D-8AA4-4FE0-AB1E-02775F35AE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0BAF41-5ABE-450E-8C92-A17D5974D362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -349,7 +349,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP3">
-            <v>200</v>
+            <v>207</v>
           </cell>
           <cell r="AQ3" t="str">
             <v>G</v>
@@ -366,7 +366,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP4">
-            <v>200</v>
+            <v>207</v>
           </cell>
           <cell r="AQ4" t="str">
             <v>D</v>
@@ -434,7 +434,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP8">
-            <v>162</v>
+            <v>161</v>
           </cell>
           <cell r="AQ8" t="str">
             <v>G</v>
@@ -502,7 +502,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP12">
-            <v>159</v>
+            <v>168</v>
           </cell>
           <cell r="AQ12" t="str">
             <v>G</v>
@@ -519,7 +519,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP13">
-            <v>159</v>
+            <v>168</v>
           </cell>
           <cell r="AQ13" t="str">
             <v>D</v>
@@ -570,7 +570,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP16">
-            <v>203</v>
+            <v>212</v>
           </cell>
           <cell r="AQ16" t="str">
             <v>D</v>
@@ -587,7 +587,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP17">
-            <v>194</v>
+            <v>202</v>
           </cell>
           <cell r="AQ17" t="str">
             <v>D</v>
@@ -604,7 +604,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP18">
-            <v>181</v>
+            <v>187</v>
           </cell>
           <cell r="AQ18" t="str">
             <v>D</v>
@@ -706,7 +706,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP24">
-            <v>159</v>
+            <v>168</v>
           </cell>
           <cell r="AQ24" t="str">
             <v>D</v>
@@ -723,7 +723,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP25">
-            <v>160</v>
+            <v>164</v>
           </cell>
           <cell r="AQ25" t="str">
             <v>D</v>
@@ -1029,7 +1029,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP43">
-            <v>203</v>
+            <v>212</v>
           </cell>
           <cell r="AQ43" t="str">
             <v>D</v>
@@ -1743,7 +1743,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP85">
-            <v>147</v>
+            <v>154</v>
           </cell>
           <cell r="AQ85" t="str">
             <v>D</v>
@@ -1811,7 +1811,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP89">
-            <v>153</v>
+            <v>162</v>
           </cell>
           <cell r="AQ89" t="str">
             <v>D</v>
@@ -2485,7 +2485,7 @@
             <v>老翁龍</v>
           </cell>
           <cell r="AN129" t="str">
-            <v>一般</v>
+            <v>超能力</v>
           </cell>
           <cell r="AO129" t="str">
             <v>N</v>
@@ -2618,7 +2618,7 @@
         </row>
         <row r="137">
           <cell r="AM137" t="str">
-            <v>喵喵</v>
+            <v>超極巨喵喵</v>
           </cell>
           <cell r="AN137" t="str">
             <v>一般</v>
@@ -2630,12 +2630,12 @@
             <v>85</v>
           </cell>
           <cell r="AQ137" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="138">
           <cell r="AM138" t="str">
-            <v>皮卡丘</v>
+            <v>超極巨皮卡丘</v>
           </cell>
           <cell r="AN138" t="str">
             <v>電</v>
@@ -2647,7 +2647,7 @@
             <v>100</v>
           </cell>
           <cell r="AQ138" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="139">
@@ -2703,36 +2703,36 @@
         </row>
         <row r="142">
           <cell r="AM142" t="str">
-            <v>超極巨喵喵</v>
+            <v>雷吉艾斯</v>
           </cell>
           <cell r="AN142" t="str">
             <v>一般</v>
           </cell>
           <cell r="AO142" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP142">
-            <v>85</v>
+            <v>153</v>
           </cell>
           <cell r="AQ142" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="143">
           <cell r="AM143" t="str">
-            <v>超極巨皮卡丘</v>
+            <v>雷吉艾斯</v>
           </cell>
           <cell r="AN143" t="str">
             <v>格鬥</v>
           </cell>
           <cell r="AO143" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP143">
-            <v>100</v>
+            <v>153</v>
           </cell>
           <cell r="AQ143" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="144">
@@ -2760,7 +2760,7 @@
             <v>龍</v>
           </cell>
           <cell r="AO145" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP145">
             <v>174</v>
@@ -2845,7 +2845,7 @@
             <v>一般</v>
           </cell>
           <cell r="AO150" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP150">
             <v>125</v>
@@ -2862,7 +2862,7 @@
             <v>格鬥</v>
           </cell>
           <cell r="AO151" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP151">
             <v>125</v>
@@ -2890,137 +2890,158 @@
         </row>
         <row r="153">
           <cell r="AM153" t="str">
-            <v/>
+            <v>風妖精</v>
           </cell>
           <cell r="AN153" t="str">
-            <v/>
-          </cell>
-          <cell r="AP153" t="str">
-            <v/>
+            <v>草</v>
+          </cell>
+          <cell r="AO153" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP153">
+            <v>141</v>
           </cell>
           <cell r="AQ153" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="154">
           <cell r="AM154" t="str">
-            <v/>
+            <v>風妖精</v>
           </cell>
           <cell r="AN154" t="str">
-            <v/>
-          </cell>
-          <cell r="AP154" t="str">
-            <v/>
+            <v>妖精</v>
+          </cell>
+          <cell r="AO154" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP154">
+            <v>141</v>
           </cell>
           <cell r="AQ154" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="155">
           <cell r="AM155" t="str">
-            <v/>
+            <v>蜂女王</v>
           </cell>
           <cell r="AN155" t="str">
-            <v/>
-          </cell>
-          <cell r="AP155" t="str">
-            <v/>
+            <v>蟲</v>
+          </cell>
+          <cell r="AO155" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP155">
+            <v>130</v>
           </cell>
           <cell r="AQ155" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="156">
           <cell r="AM156" t="str">
-            <v/>
+            <v>蜂女王</v>
           </cell>
           <cell r="AN156" t="str">
-            <v/>
-          </cell>
-          <cell r="AP156" t="str">
-            <v/>
+            <v>飛行</v>
+          </cell>
+          <cell r="AO156" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP156">
+            <v>130</v>
           </cell>
           <cell r="AQ156" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="157">
           <cell r="AM157" t="str">
-            <v/>
+            <v>蜂女王</v>
           </cell>
           <cell r="AN157" t="str">
-            <v/>
-          </cell>
-          <cell r="AP157" t="str">
-            <v/>
+            <v>毒</v>
+          </cell>
+          <cell r="AO157" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="AP157">
+            <v>130</v>
           </cell>
           <cell r="AQ157" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="158">
           <cell r="AM158" t="str">
-            <v/>
+            <v>電擊魔獸</v>
           </cell>
           <cell r="AN158" t="str">
-            <v/>
-          </cell>
-          <cell r="AP158" t="str">
-            <v/>
+            <v>電</v>
+          </cell>
+          <cell r="AO158" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP158">
+            <v>209</v>
           </cell>
           <cell r="AQ158" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="159">
           <cell r="AM159" t="str">
-            <v/>
+            <v>電擊魔獸</v>
           </cell>
           <cell r="AN159" t="str">
-            <v/>
-          </cell>
-          <cell r="AP159" t="str">
-            <v/>
+            <v>格鬥</v>
+          </cell>
+          <cell r="AO159" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="AP159">
+            <v>209</v>
           </cell>
           <cell r="AQ159" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="160">
           <cell r="AM160" t="str">
-            <v/>
+            <v>貓頭夜鷹</v>
           </cell>
           <cell r="AN160" t="str">
-            <v/>
-          </cell>
-          <cell r="AP160" t="str">
-            <v/>
+            <v>飛行</v>
+          </cell>
+          <cell r="AO160" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP160">
+            <v>126</v>
           </cell>
           <cell r="AQ160" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="161">
           <cell r="AM161" t="str">
-            <v/>
+            <v>貓頭夜鷹</v>
           </cell>
           <cell r="AN161" t="str">
-            <v/>
-          </cell>
-          <cell r="AP161" t="str">
-            <v/>
+            <v>超能力</v>
+          </cell>
+          <cell r="AO161" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="AP161">
+            <v>126</v>
           </cell>
           <cell r="AQ161" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="162">
-          <cell r="AM162" t="str">
-            <v/>
-          </cell>
-          <cell r="AN162" t="str">
-            <v/>
-          </cell>
           <cell r="AP162" t="str">
             <v/>
           </cell>
@@ -3029,12 +3050,6 @@
           </cell>
         </row>
         <row r="163">
-          <cell r="AM163" t="str">
-            <v/>
-          </cell>
-          <cell r="AN163" t="str">
-            <v/>
-          </cell>
           <cell r="AP163" t="str">
             <v/>
           </cell>
@@ -3081,6 +3096,496 @@
             <v/>
           </cell>
           <cell r="AQ166" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="AM167" t="str">
+            <v/>
+          </cell>
+          <cell r="AN167" t="str">
+            <v/>
+          </cell>
+          <cell r="AP167" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ167" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="AM168" t="str">
+            <v/>
+          </cell>
+          <cell r="AN168" t="str">
+            <v/>
+          </cell>
+          <cell r="AP168" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ168" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="AM169" t="str">
+            <v/>
+          </cell>
+          <cell r="AN169" t="str">
+            <v/>
+          </cell>
+          <cell r="AP169" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ169" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="AM170" t="str">
+            <v/>
+          </cell>
+          <cell r="AN170" t="str">
+            <v/>
+          </cell>
+          <cell r="AP170" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ170" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="AM171" t="str">
+            <v/>
+          </cell>
+          <cell r="AN171" t="str">
+            <v/>
+          </cell>
+          <cell r="AP171" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ171" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="AM172" t="str">
+            <v/>
+          </cell>
+          <cell r="AN172" t="str">
+            <v/>
+          </cell>
+          <cell r="AP172" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ172" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="AM173" t="str">
+            <v/>
+          </cell>
+          <cell r="AN173" t="str">
+            <v/>
+          </cell>
+          <cell r="AP173" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ173" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="AM174" t="str">
+            <v/>
+          </cell>
+          <cell r="AN174" t="str">
+            <v/>
+          </cell>
+          <cell r="AP174" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ174" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="175">
+          <cell r="AM175" t="str">
+            <v/>
+          </cell>
+          <cell r="AN175" t="str">
+            <v/>
+          </cell>
+          <cell r="AP175" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ175" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="176">
+          <cell r="AM176" t="str">
+            <v/>
+          </cell>
+          <cell r="AN176" t="str">
+            <v/>
+          </cell>
+          <cell r="AP176" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ176" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="177">
+          <cell r="AM177" t="str">
+            <v/>
+          </cell>
+          <cell r="AN177" t="str">
+            <v/>
+          </cell>
+          <cell r="AP177" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ177" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="178">
+          <cell r="AM178" t="str">
+            <v/>
+          </cell>
+          <cell r="AN178" t="str">
+            <v/>
+          </cell>
+          <cell r="AP178" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ178" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="179">
+          <cell r="AM179" t="str">
+            <v/>
+          </cell>
+          <cell r="AN179" t="str">
+            <v/>
+          </cell>
+          <cell r="AP179" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ179" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="180">
+          <cell r="AM180" t="str">
+            <v/>
+          </cell>
+          <cell r="AN180" t="str">
+            <v/>
+          </cell>
+          <cell r="AP180" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ180" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="181">
+          <cell r="AM181" t="str">
+            <v/>
+          </cell>
+          <cell r="AN181" t="str">
+            <v/>
+          </cell>
+          <cell r="AP181" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ181" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="182">
+          <cell r="AM182" t="str">
+            <v/>
+          </cell>
+          <cell r="AN182" t="str">
+            <v/>
+          </cell>
+          <cell r="AP182" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ182" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="183">
+          <cell r="AM183" t="str">
+            <v/>
+          </cell>
+          <cell r="AN183" t="str">
+            <v/>
+          </cell>
+          <cell r="AP183" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ183" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="184">
+          <cell r="AM184" t="str">
+            <v/>
+          </cell>
+          <cell r="AN184" t="str">
+            <v/>
+          </cell>
+          <cell r="AP184" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ184" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="185">
+          <cell r="AM185" t="str">
+            <v/>
+          </cell>
+          <cell r="AN185" t="str">
+            <v/>
+          </cell>
+          <cell r="AP185" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ185" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="186">
+          <cell r="AM186" t="str">
+            <v/>
+          </cell>
+          <cell r="AN186" t="str">
+            <v/>
+          </cell>
+          <cell r="AP186" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ186" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="187">
+          <cell r="AM187" t="str">
+            <v/>
+          </cell>
+          <cell r="AN187" t="str">
+            <v/>
+          </cell>
+          <cell r="AP187" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ187" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="188">
+          <cell r="AM188" t="str">
+            <v/>
+          </cell>
+          <cell r="AN188" t="str">
+            <v/>
+          </cell>
+          <cell r="AP188" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ188" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="189">
+          <cell r="AM189" t="str">
+            <v/>
+          </cell>
+          <cell r="AN189" t="str">
+            <v/>
+          </cell>
+          <cell r="AP189" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ189" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="190">
+          <cell r="AM190" t="str">
+            <v/>
+          </cell>
+          <cell r="AN190" t="str">
+            <v/>
+          </cell>
+          <cell r="AP190" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ190" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="191">
+          <cell r="AM191" t="str">
+            <v/>
+          </cell>
+          <cell r="AN191" t="str">
+            <v/>
+          </cell>
+          <cell r="AP191" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ191" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="192">
+          <cell r="AM192" t="str">
+            <v/>
+          </cell>
+          <cell r="AN192" t="str">
+            <v/>
+          </cell>
+          <cell r="AP192" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ192" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="193">
+          <cell r="AM193" t="str">
+            <v/>
+          </cell>
+          <cell r="AN193" t="str">
+            <v/>
+          </cell>
+          <cell r="AP193" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ193" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="194">
+          <cell r="AM194" t="str">
+            <v/>
+          </cell>
+          <cell r="AN194" t="str">
+            <v/>
+          </cell>
+          <cell r="AP194" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ194" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="195">
+          <cell r="AM195" t="str">
+            <v/>
+          </cell>
+          <cell r="AN195" t="str">
+            <v/>
+          </cell>
+          <cell r="AP195" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ195" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="196">
+          <cell r="AM196" t="str">
+            <v/>
+          </cell>
+          <cell r="AN196" t="str">
+            <v/>
+          </cell>
+          <cell r="AP196" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ196" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="197">
+          <cell r="AM197" t="str">
+            <v/>
+          </cell>
+          <cell r="AN197" t="str">
+            <v/>
+          </cell>
+          <cell r="AP197" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ197" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="198">
+          <cell r="AM198" t="str">
+            <v/>
+          </cell>
+          <cell r="AN198" t="str">
+            <v/>
+          </cell>
+          <cell r="AP198" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ198" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="199">
+          <cell r="AM199" t="str">
+            <v/>
+          </cell>
+          <cell r="AN199" t="str">
+            <v/>
+          </cell>
+          <cell r="AP199" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ199" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="200">
+          <cell r="AM200" t="str">
+            <v/>
+          </cell>
+          <cell r="AN200" t="str">
+            <v/>
+          </cell>
+          <cell r="AP200" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ200" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="201">
+          <cell r="AM201" t="str">
+            <v/>
+          </cell>
+          <cell r="AN201" t="str">
+            <v/>
+          </cell>
+          <cell r="AP201" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ201" t="str">
             <v/>
           </cell>
         </row>
@@ -3359,7 +3864,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AB200"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.65" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
@@ -3448,7 +3953,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:28" ht="16.3" x14ac:dyDescent="0.3">
       <c r="B2" s="13" t="str">
         <f>IF([1]攻守數據!AM3 = "", "", [1]攻守數據!AM3)</f>
         <v>超極巨轟擂金剛猩</v>
@@ -3463,7 +3968,7 @@
       </c>
       <c r="E2" s="13">
         <f>IF([1]攻守數據!AP3 = "", "", [1]攻守數據!AP3)</f>
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="F2" s="13" t="str">
         <f>IF([1]攻守數據!AQ3 = "", "", [1]攻守數據!AQ3)</f>
@@ -3545,7 +4050,7 @@
       </c>
       <c r="E3" s="13">
         <f>IF([1]攻守數據!AP4 = "", "", [1]攻守數據!AP4)</f>
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="F3" s="13" t="str">
         <f>IF([1]攻守數據!AQ4 = "", "", [1]攻守數據!AQ4)</f>
@@ -3612,7 +4117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:28" ht="16.3" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="str">
         <f>IF([1]攻守數據!AM5 = "", "", [1]攻守數據!AM5)</f>
         <v>超極巨怪力</v>
@@ -3873,7 +4378,7 @@
       </c>
       <c r="E7" s="13">
         <f>IF([1]攻守數據!AP8 = "", "", [1]攻守數據!AP8)</f>
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F7" s="13" t="str">
         <f>IF([1]攻守數據!AQ8 = "", "", [1]攻守數據!AQ8)</f>
@@ -3940,7 +4445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:28" ht="16.3" x14ac:dyDescent="0.3">
       <c r="B8" s="13" t="str">
         <f>IF([1]攻守數據!AM9 = "", "", [1]攻守數據!AM9)</f>
         <v>超極巨顫弦蠑螈</v>
@@ -4022,7 +4527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:28" ht="16.3" x14ac:dyDescent="0.3">
       <c r="B9" s="13" t="str">
         <f>IF([1]攻守數據!AM10 = "", "", [1]攻守數據!AM10)</f>
         <v>顫弦蠑螈</v>
@@ -4104,7 +4609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:28" ht="16.3" x14ac:dyDescent="0.3">
       <c r="B10" s="13" t="str">
         <f>IF([1]攻守數據!AM11 = "", "", [1]攻守數據!AM11)</f>
         <v>顫弦蠑螈</v>
@@ -4186,7 +4691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:28" ht="16.3" x14ac:dyDescent="0.3">
       <c r="B11" s="13" t="str">
         <f>IF([1]攻守數據!AM12 = "", "", [1]攻守數據!AM12)</f>
         <v>超極巨妙蛙花</v>
@@ -4201,7 +4706,7 @@
       </c>
       <c r="E11" s="13">
         <f>IF([1]攻守數據!AP12 = "", "", [1]攻守數據!AP12)</f>
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="F11" s="13" t="str">
         <f>IF([1]攻守數據!AQ12 = "", "", [1]攻守數據!AQ12)</f>
@@ -4283,7 +4788,7 @@
       </c>
       <c r="E12" s="13">
         <f>IF([1]攻守數據!AP13 = "", "", [1]攻守數據!AP13)</f>
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="F12" s="13" t="str">
         <f>IF([1]攻守數據!AQ13 = "", "", [1]攻守數據!AQ13)</f>
@@ -4514,7 +5019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:28" ht="16.3" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="str">
         <f>IF([1]攻守數據!AM16 = "", "", [1]攻守數據!AM16)</f>
         <v>閃電鳥</v>
@@ -4529,7 +5034,7 @@
       </c>
       <c r="E15" s="13">
         <f>IF([1]攻守數據!AP16 = "", "", [1]攻守數據!AP16)</f>
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="F15" s="13" t="str">
         <f>IF([1]攻守數據!AQ16 = "", "", [1]攻守數據!AQ16)</f>
@@ -4596,7 +5101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:28" ht="16.3" x14ac:dyDescent="0.3">
       <c r="B16" s="13" t="str">
         <f>IF([1]攻守數據!AM17 = "", "", [1]攻守數據!AM17)</f>
         <v>雷公</v>
@@ -4611,7 +5116,7 @@
       </c>
       <c r="E16" s="13">
         <f>IF([1]攻守數據!AP17 = "", "", [1]攻守數據!AP17)</f>
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="F16" s="13" t="str">
         <f>IF([1]攻守數據!AQ17 = "", "", [1]攻守數據!AQ17)</f>
@@ -4693,7 +5198,7 @@
       </c>
       <c r="E17" s="13">
         <f>IF([1]攻守數據!AP18 = "", "", [1]攻守數據!AP18)</f>
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F17" s="13" t="str">
         <f>IF([1]攻守數據!AQ18 = "", "", [1]攻守數據!AQ18)</f>
@@ -5065,7 +5570,7 @@
       </c>
       <c r="E23" s="13">
         <f>IF([1]攻守數據!AP24 = "", "", [1]攻守數據!AP24)</f>
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="F23" s="13" t="str">
         <f>IF([1]攻守數據!AQ24 = "", "", [1]攻守數據!AQ24)</f>
@@ -5087,7 +5592,7 @@
       </c>
       <c r="E24" s="13">
         <f>IF([1]攻守數據!AP25 = "", "", [1]攻守數據!AP25)</f>
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F24" s="13" t="str">
         <f>IF([1]攻守數據!AQ25 = "", "", [1]攻守數據!AQ25)</f>
@@ -5483,7 +5988,7 @@
       </c>
       <c r="E42" s="13">
         <f>IF([1]攻守數據!AP43 = "", "", [1]攻守數據!AP43)</f>
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="F42" s="13" t="str">
         <f>IF([1]攻守數據!AQ43 = "", "", [1]攻守數據!AQ43)</f>
@@ -6407,7 +6912,7 @@
       </c>
       <c r="E84" s="13">
         <f>IF([1]攻守數據!AP85 = "", "", [1]攻守數據!AP85)</f>
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F84" s="13" t="str">
         <f>IF([1]攻守數據!AQ85 = "", "", [1]攻守數據!AQ85)</f>
@@ -6495,7 +7000,7 @@
       </c>
       <c r="E88" s="13">
         <f>IF([1]攻守數據!AP89 = "", "", [1]攻守數據!AP89)</f>
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F88" s="13" t="str">
         <f>IF([1]攻守數據!AQ89 = "", "", [1]攻守數據!AQ89)</f>
@@ -7367,7 +7872,7 @@
       </c>
       <c r="C128" s="13" t="str">
         <f>IF([1]攻守數據!AN129 = "", "", [1]攻守數據!AN129)</f>
-        <v>一般</v>
+        <v>超能力</v>
       </c>
       <c r="D128" s="13" t="str">
         <f>IF([1]攻守數據!AO129 = "", "", [1]攻守數據!AO129)</f>
@@ -7539,7 +8044,7 @@
     <row r="136" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B136" s="13" t="str">
         <f>IF([1]攻守數據!AM137 = "", "", [1]攻守數據!AM137)</f>
-        <v>喵喵</v>
+        <v>超極巨喵喵</v>
       </c>
       <c r="C136" s="13" t="str">
         <f>IF([1]攻守數據!AN137 = "", "", [1]攻守數據!AN137)</f>
@@ -7555,13 +8060,13 @@
       </c>
       <c r="F136" s="13" t="str">
         <f>IF([1]攻守數據!AQ137 = "", "", [1]攻守數據!AQ137)</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="137" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B137" s="13" t="str">
         <f>IF([1]攻守數據!AM138 = "", "", [1]攻守數據!AM138)</f>
-        <v>皮卡丘</v>
+        <v>超極巨皮卡丘</v>
       </c>
       <c r="C137" s="13" t="str">
         <f>IF([1]攻守數據!AN138 = "", "", [1]攻守數據!AN138)</f>
@@ -7577,7 +8082,7 @@
       </c>
       <c r="F137" s="13" t="str">
         <f>IF([1]攻守數據!AQ138 = "", "", [1]攻守數據!AQ138)</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="138" spans="2:6" x14ac:dyDescent="0.3">
@@ -7649,7 +8154,7 @@
     <row r="141" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B141" s="13" t="str">
         <f>IF([1]攻守數據!AM142 = "", "", [1]攻守數據!AM142)</f>
-        <v>超極巨喵喵</v>
+        <v>雷吉艾斯</v>
       </c>
       <c r="C141" s="13" t="str">
         <f>IF([1]攻守數據!AN142 = "", "", [1]攻守數據!AN142)</f>
@@ -7657,21 +8162,21 @@
       </c>
       <c r="D141" s="13" t="str">
         <f>IF([1]攻守數據!AO142 = "", "", [1]攻守數據!AO142)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E141" s="13">
         <f>IF([1]攻守數據!AP142 = "", "", [1]攻守數據!AP142)</f>
-        <v>85</v>
+        <v>153</v>
       </c>
       <c r="F141" s="13" t="str">
         <f>IF([1]攻守數據!AQ142 = "", "", [1]攻守數據!AQ142)</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="142" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B142" s="13" t="str">
         <f>IF([1]攻守數據!AM143 = "", "", [1]攻守數據!AM143)</f>
-        <v>超極巨皮卡丘</v>
+        <v>雷吉艾斯</v>
       </c>
       <c r="C142" s="13" t="str">
         <f>IF([1]攻守數據!AN143 = "", "", [1]攻守數據!AN143)</f>
@@ -7679,15 +8184,15 @@
       </c>
       <c r="D142" s="13" t="str">
         <f>IF([1]攻守數據!AO143 = "", "", [1]攻守數據!AO143)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E142" s="13">
         <f>IF([1]攻守數據!AP143 = "", "", [1]攻守數據!AP143)</f>
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="F142" s="13" t="str">
         <f>IF([1]攻守數據!AQ143 = "", "", [1]攻守數據!AQ143)</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="143" spans="2:6" x14ac:dyDescent="0.3">
@@ -7723,7 +8228,7 @@
       </c>
       <c r="D144" s="13" t="str">
         <f>IF([1]攻守數據!AO145 = "", "", [1]攻守數據!AO145)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E144" s="13">
         <f>IF([1]攻守數據!AP145 = "", "", [1]攻守數據!AP145)</f>
@@ -7833,7 +8338,7 @@
       </c>
       <c r="D149" s="13" t="str">
         <f>IF([1]攻守數據!AO150 = "", "", [1]攻守數據!AO150)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E149" s="13">
         <f>IF([1]攻守數據!AP150 = "", "", [1]攻守數據!AP150)</f>
@@ -7855,7 +8360,7 @@
       </c>
       <c r="D150" s="13" t="str">
         <f>IF([1]攻守數據!AO151 = "", "", [1]攻守數據!AO151)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E150" s="13">
         <f>IF([1]攻守數據!AP151 = "", "", [1]攻守數據!AP151)</f>
@@ -7891,199 +8396,199 @@
     <row r="152" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B152" s="13" t="str">
         <f>IF([1]攻守數據!AM153 = "", "", [1]攻守數據!AM153)</f>
-        <v/>
+        <v>風妖精</v>
       </c>
       <c r="C152" s="13" t="str">
         <f>IF([1]攻守數據!AN153 = "", "", [1]攻守數據!AN153)</f>
-        <v/>
+        <v>草</v>
       </c>
       <c r="D152" s="13" t="str">
         <f>IF([1]攻守數據!AO153 = "", "", [1]攻守數據!AO153)</f>
-        <v/>
-      </c>
-      <c r="E152" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E152" s="13">
         <f>IF([1]攻守數據!AP153 = "", "", [1]攻守數據!AP153)</f>
-        <v/>
+        <v>141</v>
       </c>
       <c r="F152" s="13" t="str">
         <f>IF([1]攻守數據!AQ153 = "", "", [1]攻守數據!AQ153)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="153" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B153" s="13" t="str">
         <f>IF([1]攻守數據!AM154 = "", "", [1]攻守數據!AM154)</f>
-        <v/>
+        <v>風妖精</v>
       </c>
       <c r="C153" s="13" t="str">
         <f>IF([1]攻守數據!AN154 = "", "", [1]攻守數據!AN154)</f>
-        <v/>
+        <v>妖精</v>
       </c>
       <c r="D153" s="13" t="str">
         <f>IF([1]攻守數據!AO154 = "", "", [1]攻守數據!AO154)</f>
-        <v/>
-      </c>
-      <c r="E153" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E153" s="13">
         <f>IF([1]攻守數據!AP154 = "", "", [1]攻守數據!AP154)</f>
-        <v/>
+        <v>141</v>
       </c>
       <c r="F153" s="13" t="str">
         <f>IF([1]攻守數據!AQ154 = "", "", [1]攻守數據!AQ154)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="154" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B154" s="13" t="str">
         <f>IF([1]攻守數據!AM155 = "", "", [1]攻守數據!AM155)</f>
-        <v/>
+        <v>蜂女王</v>
       </c>
       <c r="C154" s="13" t="str">
         <f>IF([1]攻守數據!AN155 = "", "", [1]攻守數據!AN155)</f>
-        <v/>
+        <v>蟲</v>
       </c>
       <c r="D154" s="13" t="str">
         <f>IF([1]攻守數據!AO155 = "", "", [1]攻守數據!AO155)</f>
-        <v/>
-      </c>
-      <c r="E154" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E154" s="13">
         <f>IF([1]攻守數據!AP155 = "", "", [1]攻守數據!AP155)</f>
-        <v/>
+        <v>130</v>
       </c>
       <c r="F154" s="13" t="str">
         <f>IF([1]攻守數據!AQ155 = "", "", [1]攻守數據!AQ155)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B155" s="13" t="str">
         <f>IF([1]攻守數據!AM156 = "", "", [1]攻守數據!AM156)</f>
-        <v/>
+        <v>蜂女王</v>
       </c>
       <c r="C155" s="13" t="str">
         <f>IF([1]攻守數據!AN156 = "", "", [1]攻守數據!AN156)</f>
-        <v/>
+        <v>飛行</v>
       </c>
       <c r="D155" s="13" t="str">
         <f>IF([1]攻守數據!AO156 = "", "", [1]攻守數據!AO156)</f>
-        <v/>
-      </c>
-      <c r="E155" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E155" s="13">
         <f>IF([1]攻守數據!AP156 = "", "", [1]攻守數據!AP156)</f>
-        <v/>
+        <v>130</v>
       </c>
       <c r="F155" s="13" t="str">
         <f>IF([1]攻守數據!AQ156 = "", "", [1]攻守數據!AQ156)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="156" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B156" s="13" t="str">
         <f>IF([1]攻守數據!AM157 = "", "", [1]攻守數據!AM157)</f>
-        <v/>
+        <v>蜂女王</v>
       </c>
       <c r="C156" s="13" t="str">
         <f>IF([1]攻守數據!AN157 = "", "", [1]攻守數據!AN157)</f>
-        <v/>
+        <v>毒</v>
       </c>
       <c r="D156" s="13" t="str">
         <f>IF([1]攻守數據!AO157 = "", "", [1]攻守數據!AO157)</f>
-        <v/>
-      </c>
-      <c r="E156" s="13" t="str">
+        <v>N</v>
+      </c>
+      <c r="E156" s="13">
         <f>IF([1]攻守數據!AP157 = "", "", [1]攻守數據!AP157)</f>
-        <v/>
+        <v>130</v>
       </c>
       <c r="F156" s="13" t="str">
         <f>IF([1]攻守數據!AQ157 = "", "", [1]攻守數據!AQ157)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="157" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B157" s="13" t="str">
         <f>IF([1]攻守數據!AM158 = "", "", [1]攻守數據!AM158)</f>
-        <v/>
+        <v>電擊魔獸</v>
       </c>
       <c r="C157" s="13" t="str">
         <f>IF([1]攻守數據!AN158 = "", "", [1]攻守數據!AN158)</f>
-        <v/>
+        <v>電</v>
       </c>
       <c r="D157" s="13" t="str">
         <f>IF([1]攻守數據!AO158 = "", "", [1]攻守數據!AO158)</f>
-        <v/>
-      </c>
-      <c r="E157" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E157" s="13">
         <f>IF([1]攻守數據!AP158 = "", "", [1]攻守數據!AP158)</f>
-        <v/>
+        <v>209</v>
       </c>
       <c r="F157" s="13" t="str">
         <f>IF([1]攻守數據!AQ158 = "", "", [1]攻守數據!AQ158)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="158" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B158" s="13" t="str">
         <f>IF([1]攻守數據!AM159 = "", "", [1]攻守數據!AM159)</f>
-        <v/>
+        <v>電擊魔獸</v>
       </c>
       <c r="C158" s="13" t="str">
         <f>IF([1]攻守數據!AN159 = "", "", [1]攻守數據!AN159)</f>
-        <v/>
+        <v>格鬥</v>
       </c>
       <c r="D158" s="13" t="str">
         <f>IF([1]攻守數據!AO159 = "", "", [1]攻守數據!AO159)</f>
-        <v/>
-      </c>
-      <c r="E158" s="13" t="str">
+        <v>N</v>
+      </c>
+      <c r="E158" s="13">
         <f>IF([1]攻守數據!AP159 = "", "", [1]攻守數據!AP159)</f>
-        <v/>
+        <v>209</v>
       </c>
       <c r="F158" s="13" t="str">
         <f>IF([1]攻守數據!AQ159 = "", "", [1]攻守數據!AQ159)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="159" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B159" s="13" t="str">
         <f>IF([1]攻守數據!AM160 = "", "", [1]攻守數據!AM160)</f>
-        <v/>
+        <v>貓頭夜鷹</v>
       </c>
       <c r="C159" s="13" t="str">
         <f>IF([1]攻守數據!AN160 = "", "", [1]攻守數據!AN160)</f>
-        <v/>
+        <v>飛行</v>
       </c>
       <c r="D159" s="13" t="str">
         <f>IF([1]攻守數據!AO160 = "", "", [1]攻守數據!AO160)</f>
-        <v/>
-      </c>
-      <c r="E159" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E159" s="13">
         <f>IF([1]攻守數據!AP160 = "", "", [1]攻守數據!AP160)</f>
-        <v/>
+        <v>126</v>
       </c>
       <c r="F159" s="13" t="str">
         <f>IF([1]攻守數據!AQ160 = "", "", [1]攻守數據!AQ160)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="160" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B160" s="13" t="str">
         <f>IF([1]攻守數據!AM161 = "", "", [1]攻守數據!AM161)</f>
-        <v/>
+        <v>貓頭夜鷹</v>
       </c>
       <c r="C160" s="13" t="str">
         <f>IF([1]攻守數據!AN161 = "", "", [1]攻守數據!AN161)</f>
-        <v/>
+        <v>超能力</v>
       </c>
       <c r="D160" s="13" t="str">
         <f>IF([1]攻守數據!AO161 = "", "", [1]攻守數據!AO161)</f>
-        <v/>
-      </c>
-      <c r="E160" s="13" t="str">
+        <v>N</v>
+      </c>
+      <c r="E160" s="13">
         <f>IF([1]攻守數據!AP161 = "", "", [1]攻守數據!AP161)</f>
-        <v/>
+        <v>126</v>
       </c>
       <c r="F160" s="13" t="str">
         <f>IF([1]攻守數據!AQ161 = "", "", [1]攻守數據!AQ161)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="161" spans="2:6" x14ac:dyDescent="0.3">

--- a/Att.xlsx
+++ b/Att.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\寶可夢\Pokemon_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0BAF41-5ABE-450E-8C92-A17D5974D362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5043B545-F74C-4176-B51B-1378F27E4B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3042,89 +3042,122 @@
           </cell>
         </row>
         <row r="162">
-          <cell r="AP162" t="str">
-            <v/>
+          <cell r="AM162" t="str">
+            <v>暴鯉龍</v>
+          </cell>
+          <cell r="AN162" t="str">
+            <v>水</v>
+          </cell>
+          <cell r="AO162" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP162">
+            <v>199</v>
           </cell>
           <cell r="AQ162" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="163">
-          <cell r="AP163" t="str">
-            <v/>
+          <cell r="AM163" t="str">
+            <v>暴鯉龍</v>
+          </cell>
+          <cell r="AN163" t="str">
+            <v>惡</v>
+          </cell>
+          <cell r="AO163" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP163">
+            <v>199</v>
           </cell>
           <cell r="AQ163" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="164">
           <cell r="AM164" t="str">
-            <v/>
+            <v>暴鯉龍</v>
           </cell>
           <cell r="AN164" t="str">
-            <v/>
-          </cell>
-          <cell r="AP164" t="str">
-            <v/>
+            <v>龍</v>
+          </cell>
+          <cell r="AO164" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="AP164">
+            <v>199</v>
           </cell>
           <cell r="AQ164" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="165">
           <cell r="AM165" t="str">
-            <v/>
+            <v>三首惡龍</v>
           </cell>
           <cell r="AN165" t="str">
-            <v/>
-          </cell>
-          <cell r="AP165" t="str">
-            <v/>
+            <v>惡</v>
+          </cell>
+          <cell r="AO165" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP165">
+            <v>214</v>
           </cell>
           <cell r="AQ165" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="166">
           <cell r="AM166" t="str">
-            <v/>
+            <v>三首惡龍</v>
           </cell>
           <cell r="AN166" t="str">
-            <v/>
-          </cell>
-          <cell r="AP166" t="str">
-            <v/>
+            <v>龍</v>
+          </cell>
+          <cell r="AO166" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP166">
+            <v>214</v>
           </cell>
           <cell r="AQ166" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="167">
           <cell r="AM167" t="str">
-            <v/>
+            <v>美納斯</v>
           </cell>
           <cell r="AN167" t="str">
-            <v/>
-          </cell>
-          <cell r="AP167" t="str">
-            <v/>
+            <v>水</v>
+          </cell>
+          <cell r="AO167" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP167">
+            <v>164</v>
           </cell>
           <cell r="AQ167" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="168">
           <cell r="AM168" t="str">
-            <v/>
+            <v>美納斯</v>
           </cell>
           <cell r="AN168" t="str">
-            <v/>
-          </cell>
-          <cell r="AP168" t="str">
-            <v/>
+            <v>龍</v>
+          </cell>
+          <cell r="AO168" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="AP168">
+            <v>164</v>
           </cell>
           <cell r="AQ168" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="169">
@@ -3137,9 +3170,6 @@
           <cell r="AP169" t="str">
             <v/>
           </cell>
-          <cell r="AQ169" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="170">
           <cell r="AM170" t="str">
@@ -3151,9 +3181,6 @@
           <cell r="AP170" t="str">
             <v/>
           </cell>
-          <cell r="AQ170" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="171">
           <cell r="AM171" t="str">
@@ -3165,9 +3192,6 @@
           <cell r="AP171" t="str">
             <v/>
           </cell>
-          <cell r="AQ171" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="172">
           <cell r="AM172" t="str">
@@ -3179,9 +3203,6 @@
           <cell r="AP172" t="str">
             <v/>
           </cell>
-          <cell r="AQ172" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="173">
           <cell r="AM173" t="str">
@@ -3193,9 +3214,6 @@
           <cell r="AP173" t="str">
             <v/>
           </cell>
-          <cell r="AQ173" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="174">
           <cell r="AM174" t="str">
@@ -3207,9 +3225,6 @@
           <cell r="AP174" t="str">
             <v/>
           </cell>
-          <cell r="AQ174" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="175">
           <cell r="AM175" t="str">
@@ -3219,9 +3234,6 @@
             <v/>
           </cell>
           <cell r="AP175" t="str">
-            <v/>
-          </cell>
-          <cell r="AQ175" t="str">
             <v/>
           </cell>
         </row>
@@ -8594,155 +8606,155 @@
     <row r="161" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B161" s="13" t="str">
         <f>IF([1]攻守數據!AM162 = "", "", [1]攻守數據!AM162)</f>
-        <v/>
+        <v>暴鯉龍</v>
       </c>
       <c r="C161" s="13" t="str">
         <f>IF([1]攻守數據!AN162 = "", "", [1]攻守數據!AN162)</f>
-        <v/>
+        <v>水</v>
       </c>
       <c r="D161" s="13" t="str">
         <f>IF([1]攻守數據!AO162 = "", "", [1]攻守數據!AO162)</f>
-        <v/>
-      </c>
-      <c r="E161" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E161" s="13">
         <f>IF([1]攻守數據!AP162 = "", "", [1]攻守數據!AP162)</f>
-        <v/>
+        <v>199</v>
       </c>
       <c r="F161" s="13" t="str">
         <f>IF([1]攻守數據!AQ162 = "", "", [1]攻守數據!AQ162)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="162" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B162" s="13" t="str">
         <f>IF([1]攻守數據!AM163 = "", "", [1]攻守數據!AM163)</f>
-        <v/>
+        <v>暴鯉龍</v>
       </c>
       <c r="C162" s="13" t="str">
         <f>IF([1]攻守數據!AN163 = "", "", [1]攻守數據!AN163)</f>
-        <v/>
+        <v>惡</v>
       </c>
       <c r="D162" s="13" t="str">
         <f>IF([1]攻守數據!AO163 = "", "", [1]攻守數據!AO163)</f>
-        <v/>
-      </c>
-      <c r="E162" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E162" s="13">
         <f>IF([1]攻守數據!AP163 = "", "", [1]攻守數據!AP163)</f>
-        <v/>
+        <v>199</v>
       </c>
       <c r="F162" s="13" t="str">
         <f>IF([1]攻守數據!AQ163 = "", "", [1]攻守數據!AQ163)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="163" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B163" s="13" t="str">
         <f>IF([1]攻守數據!AM164 = "", "", [1]攻守數據!AM164)</f>
-        <v/>
+        <v>暴鯉龍</v>
       </c>
       <c r="C163" s="13" t="str">
         <f>IF([1]攻守數據!AN164 = "", "", [1]攻守數據!AN164)</f>
-        <v/>
+        <v>龍</v>
       </c>
       <c r="D163" s="13" t="str">
         <f>IF([1]攻守數據!AO164 = "", "", [1]攻守數據!AO164)</f>
-        <v/>
-      </c>
-      <c r="E163" s="13" t="str">
+        <v>N</v>
+      </c>
+      <c r="E163" s="13">
         <f>IF([1]攻守數據!AP164 = "", "", [1]攻守數據!AP164)</f>
-        <v/>
+        <v>199</v>
       </c>
       <c r="F163" s="13" t="str">
         <f>IF([1]攻守數據!AQ164 = "", "", [1]攻守數據!AQ164)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B164" s="13" t="str">
         <f>IF([1]攻守數據!AM165 = "", "", [1]攻守數據!AM165)</f>
-        <v/>
+        <v>三首惡龍</v>
       </c>
       <c r="C164" s="13" t="str">
         <f>IF([1]攻守數據!AN165 = "", "", [1]攻守數據!AN165)</f>
-        <v/>
+        <v>惡</v>
       </c>
       <c r="D164" s="13" t="str">
         <f>IF([1]攻守數據!AO165 = "", "", [1]攻守數據!AO165)</f>
-        <v/>
-      </c>
-      <c r="E164" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E164" s="13">
         <f>IF([1]攻守數據!AP165 = "", "", [1]攻守數據!AP165)</f>
-        <v/>
+        <v>214</v>
       </c>
       <c r="F164" s="13" t="str">
         <f>IF([1]攻守數據!AQ165 = "", "", [1]攻守數據!AQ165)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="165" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B165" s="13" t="str">
         <f>IF([1]攻守數據!AM166 = "", "", [1]攻守數據!AM166)</f>
-        <v/>
+        <v>三首惡龍</v>
       </c>
       <c r="C165" s="13" t="str">
         <f>IF([1]攻守數據!AN166 = "", "", [1]攻守數據!AN166)</f>
-        <v/>
+        <v>龍</v>
       </c>
       <c r="D165" s="13" t="str">
         <f>IF([1]攻守數據!AO166 = "", "", [1]攻守數據!AO166)</f>
-        <v/>
-      </c>
-      <c r="E165" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E165" s="13">
         <f>IF([1]攻守數據!AP166 = "", "", [1]攻守數據!AP166)</f>
-        <v/>
+        <v>214</v>
       </c>
       <c r="F165" s="13" t="str">
         <f>IF([1]攻守數據!AQ166 = "", "", [1]攻守數據!AQ166)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="166" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B166" s="13" t="str">
         <f>IF([1]攻守數據!AM167 = "", "", [1]攻守數據!AM167)</f>
-        <v/>
+        <v>美納斯</v>
       </c>
       <c r="C166" s="13" t="str">
         <f>IF([1]攻守數據!AN167 = "", "", [1]攻守數據!AN167)</f>
-        <v/>
+        <v>水</v>
       </c>
       <c r="D166" s="13" t="str">
         <f>IF([1]攻守數據!AO167 = "", "", [1]攻守數據!AO167)</f>
-        <v/>
-      </c>
-      <c r="E166" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E166" s="13">
         <f>IF([1]攻守數據!AP167 = "", "", [1]攻守數據!AP167)</f>
-        <v/>
+        <v>164</v>
       </c>
       <c r="F166" s="13" t="str">
         <f>IF([1]攻守數據!AQ167 = "", "", [1]攻守數據!AQ167)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="167" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B167" s="13" t="str">
         <f>IF([1]攻守數據!AM168 = "", "", [1]攻守數據!AM168)</f>
-        <v/>
+        <v>美納斯</v>
       </c>
       <c r="C167" s="13" t="str">
         <f>IF([1]攻守數據!AN168 = "", "", [1]攻守數據!AN168)</f>
-        <v/>
+        <v>龍</v>
       </c>
       <c r="D167" s="13" t="str">
         <f>IF([1]攻守數據!AO168 = "", "", [1]攻守數據!AO168)</f>
-        <v/>
-      </c>
-      <c r="E167" s="13" t="str">
+        <v>N</v>
+      </c>
+      <c r="E167" s="13">
         <f>IF([1]攻守數據!AP168 = "", "", [1]攻守數據!AP168)</f>
-        <v/>
+        <v>164</v>
       </c>
       <c r="F167" s="13" t="str">
         <f>IF([1]攻守數據!AQ168 = "", "", [1]攻守數據!AQ168)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="168" spans="2:6" x14ac:dyDescent="0.3">
